--- a/DataTable/내일할래_데이터테이블.xlsx
+++ b/DataTable/내일할래_데이터테이블.xlsx
@@ -11,7 +11,8 @@
     <sheet name="Stage" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Monster" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Character" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Balance" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Story" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Balance" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -513,7 +514,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:D35"/>
+  <dimension ref="B1:D38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -696,228 +697,275 @@
     <row r="17">
       <c r="B17" s="9" t="inlineStr">
         <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="C17" s="10" t="inlineStr">
+        <is>
+          <t>Story.csv</t>
+        </is>
+      </c>
+      <c r="D17" s="11" t="inlineStr">
+        <is>
+          <t>캐릭터 이야기 구매 비용, 필요 레벨, 달 자동공격 영구 강화량</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="9" t="inlineStr">
+        <is>
           <t>Balance</t>
         </is>
       </c>
-      <c r="C17" s="10" t="inlineStr">
+      <c r="C18" s="10" t="inlineStr">
         <is>
           <t>Balance.csv</t>
         </is>
       </c>
-      <c r="D17" s="11" t="inlineStr">
-        <is>
-          <t>달 자동공격 데미지·주기, 보스전 제한시간, 보스 도전 조건</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="B19" s="3" t="inlineStr">
+      <c r="D18" s="11" t="inlineStr">
+        <is>
+          <t>달 자동공격 기본 데미지·주기, 보스전 제한시간, 보스 도전 조건</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="3" t="inlineStr">
         <is>
           <t>■ 게임에서 쓰는 계산식</t>
         </is>
       </c>
-      <c r="C19" s="4" t="n"/>
-      <c r="D19" s="4" t="n"/>
-    </row>
-    <row r="20">
-      <c r="B20" s="5" t="inlineStr">
+      <c r="C20" s="4" t="n"/>
+      <c r="D20" s="4" t="n"/>
+    </row>
+    <row r="21">
+      <c r="B21" s="5" t="inlineStr">
         <is>
           <t>터치(클릭) 데미지</t>
         </is>
       </c>
-      <c r="C20" s="5" t="inlineStr">
+      <c r="C21" s="5" t="inlineStr">
         <is>
           <t>캐릭터 1명</t>
         </is>
       </c>
-      <c r="D20" s="6" t="inlineStr">
+      <c r="D21" s="6" t="inlineStr">
         <is>
           <t>기본 데미지 + (레벨 − 1) × 레벨당 데미지 증가</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="B21" s="5" t="inlineStr"/>
-      <c r="C21" s="5" t="inlineStr">
+    <row r="22">
+      <c r="B22" s="5" t="inlineStr"/>
+      <c r="C22" s="5" t="inlineStr">
         <is>
           <t>실제 클릭 데미지</t>
         </is>
       </c>
-      <c r="D21" s="6" t="inlineStr">
+      <c r="D22" s="6" t="inlineStr">
         <is>
           <t>해금된 모든 캐릭터의 위 값을 전부 더한 합계 (최소 1)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="B22" s="5" t="inlineStr">
-        <is>
-          <t>레벨업 비용</t>
-        </is>
-      </c>
-      <c r="C22" s="5" t="inlineStr">
-        <is>
-          <t>레벨 L → L+1</t>
-        </is>
-      </c>
-      <c r="D22" s="6" t="inlineStr">
-        <is>
-          <t>레벨업 기본 비용 + (L − 1) × 레벨업 비용 증가</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>달 자동공격</t>
-        </is>
-      </c>
-      <c r="C23" s="5" t="inlineStr"/>
+          <t>레벨업 비용</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>레벨 L → L+1</t>
+        </is>
+      </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>moonInterval 초마다 moonDamage 만큼 현재 몬스터에게 즉시 피해</t>
+          <t>레벨업 기본 비용 + (L − 1) × 레벨업 비용 증가</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="B24" s="5" t="inlineStr">
         <is>
+          <t>달 자동공격</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>실제 데미지</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="inlineStr">
+        <is>
+          <t>moonDamage + 구매한 이야기들의 '달 데미지 증가' 합계</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" s="5" t="inlineStr"/>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>실제 주기</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="inlineStr">
+        <is>
+          <t>moonInterval − 구매한 이야기들의 '달 주기 감소' 합계 (아무리 줄여도 최소 0.1초)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>이야기 해금</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr"/>
+      <c r="D26" s="6" t="inlineStr">
+        <is>
+          <t>그 이야기의 '캐릭터 번호'에 해당하는 캐릭터가 '필요 레벨' 이상이면 열림. 열린 뒤 꿈코인으로 구매하면 달이 영구 강화됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="5" t="inlineStr">
+        <is>
           <t>보스 도전 조건</t>
         </is>
       </c>
-      <c r="C24" s="5" t="inlineStr"/>
-      <c r="D24" s="6" t="inlineStr">
+      <c r="C27" s="5" t="inlineStr"/>
+      <c r="D27" s="6" t="inlineStr">
         <is>
           <t>일반 몬스터를 killsRequired 마리 처치하면 보스 버튼이 열림</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="B25" s="5" t="inlineStr">
+    <row r="28">
+      <c r="B28" s="5" t="inlineStr">
         <is>
           <t>보스전 제한시간</t>
         </is>
       </c>
-      <c r="C25" s="5" t="inlineStr"/>
-      <c r="D25" s="6" t="inlineStr">
+      <c r="C28" s="5" t="inlineStr"/>
+      <c r="D28" s="6" t="inlineStr">
         <is>
           <t>bossDuration 초 안에 보스를 처치해야 다음 스테이지로 이동</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="B27" s="2" t="inlineStr">
+    <row r="30">
+      <c r="B30" s="2" t="inlineStr">
         <is>
           <t>Character 시트의 [참고] 컬럼은 위 계산식을 미리 계산해 보여주는 것으로, 게임은 이 값을 읽지 않습니다.</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="B29" s="3" t="inlineStr">
+    <row r="32">
+      <c r="B32" s="3" t="inlineStr">
         <is>
           <t>■ 규칙 (지키지 않으면 반영되지 않습니다)</t>
         </is>
       </c>
-      <c r="C29" s="4" t="n"/>
-      <c r="D29" s="4" t="n"/>
-    </row>
-    <row r="30">
-      <c r="B30" s="5" t="inlineStr">
-        <is>
-          <t>2행 = 영문 키</t>
-        </is>
-      </c>
-      <c r="C30" s="5" t="inlineStr">
-        <is>
-          <t>★ 절대 건드리지 마세요</t>
-        </is>
-      </c>
-      <c r="D30" s="6" t="inlineStr">
-        <is>
-          <t>게임은 'stage / index / key' 같은 영문 이름이 있는 줄을 찾아 헤더로 씁니다. 이 줄을 바꾸거나 지우면 그 표 전체가 반영되지 않습니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="B31" s="5" t="inlineStr">
-        <is>
-          <t>1행 = 한글 제목</t>
-        </is>
-      </c>
-      <c r="C31" s="5" t="inlineStr">
-        <is>
-          <t>게임이 무시함</t>
-        </is>
-      </c>
-      <c r="D31" s="6" t="inlineStr">
-        <is>
-          <t>영문 키 줄보다 위에 있는 줄은 몇 줄이든 전부 무시됩니다. 제목을 자유롭게 고치거나 설명 줄을 더 넣어도 안전합니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="B32" s="5" t="inlineStr">
-        <is>
-          <t>3행부터 = 데이터</t>
-        </is>
-      </c>
-      <c r="C32" s="5" t="inlineStr">
-        <is>
-          <t>게임이 읽음</t>
-        </is>
-      </c>
-      <c r="D32" s="6" t="inlineStr">
-        <is>
-          <t>여기 숫자를 고치면 됩니다.</t>
-        </is>
-      </c>
+      <c r="C32" s="4" t="n"/>
+      <c r="D32" s="4" t="n"/>
     </row>
     <row r="33">
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>이미지·이름</t>
+          <t>2행 = 영문 키</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>Unity 인스펙터</t>
+          <t>★ 절대 건드리지 마세요</t>
         </is>
       </c>
       <c r="D33" s="6" t="inlineStr">
         <is>
-          <t>스프라이트, 스테이지 이름, 캐릭터 이름은 이 표가 아니라 Unity에서 관리합니다.</t>
+          <t>게임은 'stage / index / key' 같은 영문 이름이 있는 줄을 찾아 헤더로 씁니다. 이 줄을 바꾸거나 지우면 그 표 전체가 반영되지 않습니다.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>없는 항목</t>
+          <t>1행 = 한글 제목</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>무시됨</t>
+          <t>게임이 무시함</t>
         </is>
       </c>
       <c r="D34" s="6" t="inlineStr">
         <is>
-          <t>Unity 인스펙터에 없는 stage/index/캐릭터 번호를 적으면 경고만 남기고 건너뜁니다.</t>
+          <t>영문 키 줄보다 위에 있는 줄은 몇 줄이든 전부 무시됩니다. 제목을 자유롭게 고치거나 설명 줄을 더 넣어도 안전합니다.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="B35" s="5" t="inlineStr">
         <is>
+          <t>3행부터 = 데이터</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>게임이 읽음</t>
+        </is>
+      </c>
+      <c r="D35" s="6" t="inlineStr">
+        <is>
+          <t>여기 숫자를 고치면 됩니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>이미지·이름</t>
+        </is>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>Unity 인스펙터</t>
+        </is>
+      </c>
+      <c r="D36" s="6" t="inlineStr">
+        <is>
+          <t>스프라이트, 스테이지 이름, 캐릭터 이름은 이 표가 아니라 Unity에서 관리합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" s="5" t="inlineStr">
+        <is>
+          <t>없는 항목</t>
+        </is>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>무시됨</t>
+        </is>
+      </c>
+      <c r="D37" s="6" t="inlineStr">
+        <is>
+          <t>Unity 인스펙터에 없는 stage/index/캐릭터 번호를 적으면 경고만 남기고 건너뜁니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" s="5" t="inlineStr">
+        <is>
           <t>컬럼 추가</t>
         </is>
       </c>
-      <c r="C35" s="5" t="inlineStr">
+      <c r="C38" s="5" t="inlineStr">
         <is>
           <t>자유</t>
         </is>
       </c>
-      <c r="D35" s="6" t="inlineStr">
+      <c r="D38" s="6" t="inlineStr">
         <is>
           <t>게임이 모르는 컬럼(메모 등)은 그냥 무시하니 마음껏 추가해도 됩니다.</t>
         </is>
@@ -926,7 +974,7 @@
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="B10:D10"/>
-    <mergeCell ref="B27:D27"/>
+    <mergeCell ref="B30:D30"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1345,6 +1393,152 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:F5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="12" t="inlineStr">
+        <is>
+          <t>#이야기 번호</t>
+        </is>
+      </c>
+      <c r="B1" s="12" t="inlineStr">
+        <is>
+          <t>캐릭터 번호</t>
+        </is>
+      </c>
+      <c r="C1" s="12" t="inlineStr">
+        <is>
+          <t>필요 레벨</t>
+        </is>
+      </c>
+      <c r="D1" s="12" t="inlineStr">
+        <is>
+          <t>구매 비용(꿈코인)</t>
+        </is>
+      </c>
+      <c r="E1" s="12" t="inlineStr">
+        <is>
+          <t>달 데미지 증가</t>
+        </is>
+      </c>
+      <c r="F1" s="12" t="inlineStr">
+        <is>
+          <t>달 주기 감소(초)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="13" t="inlineStr">
+        <is>
+          <t>index</t>
+        </is>
+      </c>
+      <c r="B2" s="13" t="inlineStr">
+        <is>
+          <t>characterIndex</t>
+        </is>
+      </c>
+      <c r="C2" s="13" t="inlineStr">
+        <is>
+          <t>requiredLevel</t>
+        </is>
+      </c>
+      <c r="D2" s="13" t="inlineStr">
+        <is>
+          <t>cost</t>
+        </is>
+      </c>
+      <c r="E2" s="13" t="inlineStr">
+        <is>
+          <t>moonDamageBonus</t>
+        </is>
+      </c>
+      <c r="F2" s="13" t="inlineStr">
+        <is>
+          <t>moonIntervalReduction</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="B3" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="C3" s="14" t="n">
+        <v>150</v>
+      </c>
+      <c r="D3" s="14" t="n">
+        <v>500</v>
+      </c>
+      <c r="E3" s="14" t="n">
+        <v>20</v>
+      </c>
+      <c r="F3" s="14" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="B4" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" s="14" t="n">
+        <v>150</v>
+      </c>
+      <c r="D4" s="14" t="n">
+        <v>800</v>
+      </c>
+      <c r="E4" s="14" t="n">
+        <v>30</v>
+      </c>
+      <c r="F4" s="14" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="B5" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="C5" s="14" t="n">
+        <v>150</v>
+      </c>
+      <c r="D5" s="14" t="n">
+        <v>1200</v>
+      </c>
+      <c r="E5" s="14" t="n">
+        <v>40</v>
+      </c>
+      <c r="F5" s="14" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:C6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>

--- a/DataTable/내일할래_데이터테이블.xlsx
+++ b/DataTable/내일할래_데이터테이블.xlsx
@@ -12,7 +12,8 @@
     <sheet name="Monster" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Character" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Story" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Balance" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Constellation" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Balance" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -514,7 +515,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:D38"/>
+  <dimension ref="B1:D43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -714,258 +715,335 @@
     <row r="18">
       <c r="B18" s="9" t="inlineStr">
         <is>
+          <t>Constellation</t>
+        </is>
+      </c>
+      <c r="C18" s="10" t="inlineStr">
+        <is>
+          <t>Constellation.csv</t>
+        </is>
+      </c>
+      <c r="D18" s="11" t="inlineStr">
+        <is>
+          <t>별자리 구성 별 개수, 해금 스테이지, 별 구매 비용, 완성 효과</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="9" t="inlineStr">
+        <is>
           <t>Balance</t>
         </is>
       </c>
-      <c r="C18" s="10" t="inlineStr">
+      <c r="C19" s="10" t="inlineStr">
         <is>
           <t>Balance.csv</t>
         </is>
       </c>
-      <c r="D18" s="11" t="inlineStr">
+      <c r="D19" s="11" t="inlineStr">
         <is>
           <t>달 자동공격 기본 데미지·주기, 보스전 제한시간, 보스 도전 조건</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="B20" s="3" t="inlineStr">
+    <row r="21">
+      <c r="B21" s="3" t="inlineStr">
         <is>
           <t>■ 게임에서 쓰는 계산식</t>
         </is>
       </c>
-      <c r="C20" s="4" t="n"/>
-      <c r="D20" s="4" t="n"/>
-    </row>
-    <row r="21">
-      <c r="B21" s="5" t="inlineStr">
+      <c r="C21" s="4" t="n"/>
+      <c r="D21" s="4" t="n"/>
+    </row>
+    <row r="22">
+      <c r="B22" s="5" t="inlineStr">
         <is>
           <t>터치(클릭) 데미지</t>
         </is>
       </c>
-      <c r="C21" s="5" t="inlineStr">
+      <c r="C22" s="5" t="inlineStr">
         <is>
           <t>캐릭터 1명</t>
         </is>
       </c>
-      <c r="D21" s="6" t="inlineStr">
+      <c r="D22" s="6" t="inlineStr">
         <is>
           <t>기본 데미지 + (레벨 − 1) × 레벨당 데미지 증가</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="B22" s="5" t="inlineStr"/>
-      <c r="C22" s="5" t="inlineStr">
+    <row r="23">
+      <c r="B23" s="5" t="inlineStr"/>
+      <c r="C23" s="5" t="inlineStr">
         <is>
           <t>실제 클릭 데미지</t>
         </is>
       </c>
-      <c r="D22" s="6" t="inlineStr">
+      <c r="D23" s="6" t="inlineStr">
         <is>
           <t>해금된 모든 캐릭터의 위 값을 전부 더한 합계 (최소 1)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="B23" s="5" t="inlineStr">
-        <is>
-          <t>레벨업 비용</t>
-        </is>
-      </c>
-      <c r="C23" s="5" t="inlineStr">
-        <is>
-          <t>레벨 L → L+1</t>
-        </is>
-      </c>
-      <c r="D23" s="6" t="inlineStr">
-        <is>
-          <t>레벨업 기본 비용 + (L − 1) × 레벨업 비용 증가</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="B24" s="5" t="inlineStr">
         <is>
+          <t>레벨업 비용</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>레벨 L → L+1</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="inlineStr">
+        <is>
+          <t>레벨업 기본 비용 + (L − 1) × 레벨업 비용 증가</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" s="5" t="inlineStr">
+        <is>
           <t>달 자동공격</t>
         </is>
       </c>
-      <c r="C24" s="5" t="inlineStr">
+      <c r="C25" s="5" t="inlineStr">
         <is>
           <t>실제 데미지</t>
         </is>
       </c>
-      <c r="D24" s="6" t="inlineStr">
+      <c r="D25" s="6" t="inlineStr">
         <is>
           <t>moonDamage + 구매한 이야기들의 '달 데미지 증가' 합계</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="B25" s="5" t="inlineStr"/>
-      <c r="C25" s="5" t="inlineStr">
+    <row r="26">
+      <c r="B26" s="5" t="inlineStr"/>
+      <c r="C26" s="5" t="inlineStr">
         <is>
           <t>실제 주기</t>
         </is>
       </c>
-      <c r="D25" s="6" t="inlineStr">
+      <c r="D26" s="6" t="inlineStr">
         <is>
           <t>moonInterval − 구매한 이야기들의 '달 주기 감소' 합계 (아무리 줄여도 최소 0.1초)</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="B26" s="5" t="inlineStr">
-        <is>
-          <t>이야기 해금</t>
-        </is>
-      </c>
-      <c r="C26" s="5" t="inlineStr"/>
-      <c r="D26" s="6" t="inlineStr">
-        <is>
-          <t>그 이야기의 '캐릭터 번호'에 해당하는 캐릭터가 '필요 레벨' 이상이면 열림. 열린 뒤 꿈코인으로 구매하면 달이 영구 강화됨</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>보스 도전 조건</t>
+          <t>이야기 해금</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr"/>
       <c r="D27" s="6" t="inlineStr">
         <is>
-          <t>일반 몬스터를 killsRequired 마리 처치하면 보스 버튼이 열림</t>
+          <t>그 이야기의 '캐릭터 번호'에 해당하는 캐릭터가 '필요 레벨' 이상이면 열림. 열린 뒤 꿈코인으로 구매하면 달이 영구 강화됨</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>보스전 제한시간</t>
+          <t>보스 도전 조건</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr"/>
       <c r="D28" s="6" t="inlineStr">
         <is>
+          <t>일반 몬스터를 killsRequired 마리 처치하면 보스 버튼이 열림</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>보스전 제한시간</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr"/>
+      <c r="D29" s="6" t="inlineStr">
+        <is>
           <t>bossDuration 초 안에 보스를 처치해야 다음 스테이지로 이동</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>Character 시트의 [참고] 컬럼은 위 계산식을 미리 계산해 보여주는 것으로, 게임은 이 값을 읽지 않습니다.</t>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>별자리 해금</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="inlineStr"/>
+      <c r="D30" s="6" t="inlineStr">
+        <is>
+          <t>현재 스테이지가 '해금 스테이지' 이상이면 그 별자리의 별을 살 수 있음</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>별 구매 비용</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>n번째 별</t>
+        </is>
+      </c>
+      <c r="D31" s="6" t="inlineStr">
+        <is>
+          <t>별 첫 구매 비용 + (이미 산 별 개수) × 별 비용 증가</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="B32" s="3" t="inlineStr">
-        <is>
-          <t>■ 규칙 (지키지 않으면 반영되지 않습니다)</t>
-        </is>
-      </c>
-      <c r="C32" s="4" t="n"/>
-      <c r="D32" s="4" t="n"/>
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>별자리 완성</t>
+        </is>
+      </c>
+      <c r="C32" s="5" t="inlineStr"/>
+      <c r="D32" s="6" t="inlineStr">
+        <is>
+          <t>구성 별을 전부 사면 완성 → 효과 발동 + 배경에 별자리 리소스 배치</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>2행 = 영문 키</t>
+          <t>별자리 효과 종류</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>★ 절대 건드리지 마세요</t>
+          <t>effectType</t>
         </is>
       </c>
       <c r="D33" s="6" t="inlineStr">
         <is>
-          <t>게임은 'stage / index / key' 같은 영문 이름이 있는 줄을 찾아 헤더로 씁니다. 이 줄을 바꾸거나 지우면 그 표 전체가 반영되지 않습니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="B34" s="5" t="inlineStr">
-        <is>
-          <t>1행 = 한글 제목</t>
-        </is>
-      </c>
-      <c r="C34" s="5" t="inlineStr">
-        <is>
-          <t>게임이 무시함</t>
-        </is>
-      </c>
-      <c r="D34" s="6" t="inlineStr">
-        <is>
-          <t>영문 키 줄보다 위에 있는 줄은 몇 줄이든 전부 무시됩니다. 제목을 자유롭게 고치거나 설명 줄을 더 넣어도 안전합니다.</t>
+          <t>0 = 클릭 데미지 +수치 / 1 = 달 데미지 +수치 / 2 = 달 주기 −수치(초) / 3 = 꿈코인 획득 +수치(0.2 = +20%)</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="B35" s="5" t="inlineStr">
-        <is>
-          <t>3행부터 = 데이터</t>
-        </is>
-      </c>
-      <c r="C35" s="5" t="inlineStr">
-        <is>
-          <t>게임이 읽음</t>
-        </is>
-      </c>
-      <c r="D35" s="6" t="inlineStr">
-        <is>
-          <t>여기 숫자를 고치면 됩니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="B36" s="5" t="inlineStr">
-        <is>
-          <t>이미지·이름</t>
-        </is>
-      </c>
-      <c r="C36" s="5" t="inlineStr">
-        <is>
-          <t>Unity 인스펙터</t>
-        </is>
-      </c>
-      <c r="D36" s="6" t="inlineStr">
-        <is>
-          <t>스프라이트, 스테이지 이름, 캐릭터 이름은 이 표가 아니라 Unity에서 관리합니다.</t>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>Character 시트의 [참고] 컬럼은 위 계산식을 미리 계산해 보여주는 것으로, 게임은 이 값을 읽지 않습니다.</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="B37" s="5" t="inlineStr">
-        <is>
-          <t>없는 항목</t>
-        </is>
-      </c>
-      <c r="C37" s="5" t="inlineStr">
-        <is>
-          <t>무시됨</t>
-        </is>
-      </c>
-      <c r="D37" s="6" t="inlineStr">
-        <is>
-          <t>Unity 인스펙터에 없는 stage/index/캐릭터 번호를 적으면 경고만 남기고 건너뜁니다.</t>
-        </is>
-      </c>
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>■ 규칙 (지키지 않으면 반영되지 않습니다)</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="n"/>
+      <c r="D37" s="4" t="n"/>
     </row>
     <row r="38">
       <c r="B38" s="5" t="inlineStr">
         <is>
+          <t>2행 = 영문 키</t>
+        </is>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>★ 절대 건드리지 마세요</t>
+        </is>
+      </c>
+      <c r="D38" s="6" t="inlineStr">
+        <is>
+          <t>게임은 'stage / index / key' 같은 영문 이름이 있는 줄을 찾아 헤더로 씁니다. 이 줄을 바꾸거나 지우면 그 표 전체가 반영되지 않습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>1행 = 한글 제목</t>
+        </is>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>게임이 무시함</t>
+        </is>
+      </c>
+      <c r="D39" s="6" t="inlineStr">
+        <is>
+          <t>영문 키 줄보다 위에 있는 줄은 몇 줄이든 전부 무시됩니다. 제목을 자유롭게 고치거나 설명 줄을 더 넣어도 안전합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="B40" s="5" t="inlineStr">
+        <is>
+          <t>3행부터 = 데이터</t>
+        </is>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>게임이 읽음</t>
+        </is>
+      </c>
+      <c r="D40" s="6" t="inlineStr">
+        <is>
+          <t>여기 숫자를 고치면 됩니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>이미지·이름</t>
+        </is>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>Unity 인스펙터</t>
+        </is>
+      </c>
+      <c r="D41" s="6" t="inlineStr">
+        <is>
+          <t>스프라이트, 스테이지 이름, 캐릭터 이름은 이 표가 아니라 Unity에서 관리합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" s="5" t="inlineStr">
+        <is>
+          <t>없는 항목</t>
+        </is>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>무시됨</t>
+        </is>
+      </c>
+      <c r="D42" s="6" t="inlineStr">
+        <is>
+          <t>Unity 인스펙터에 없는 stage/index/캐릭터 번호를 적으면 경고만 남기고 건너뜁니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="B43" s="5" t="inlineStr">
+        <is>
           <t>컬럼 추가</t>
         </is>
       </c>
-      <c r="C38" s="5" t="inlineStr">
+      <c r="C43" s="5" t="inlineStr">
         <is>
           <t>자유</t>
         </is>
       </c>
-      <c r="D38" s="6" t="inlineStr">
+      <c r="D43" s="6" t="inlineStr">
         <is>
           <t>게임이 모르는 컬럼(메모 등)은 그냥 무시하니 마음껏 추가해도 됩니다.</t>
         </is>
@@ -974,7 +1052,7 @@
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="B10:D10"/>
-    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="B35:D35"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1539,6 +1617,438 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:H14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="12" t="inlineStr">
+        <is>
+          <t>#별자리 번호</t>
+        </is>
+      </c>
+      <c r="B1" s="12" t="inlineStr">
+        <is>
+          <t>구성 별 개수</t>
+        </is>
+      </c>
+      <c r="C1" s="12" t="inlineStr">
+        <is>
+          <t>해금 스테이지</t>
+        </is>
+      </c>
+      <c r="D1" s="12" t="inlineStr">
+        <is>
+          <t>별 첫 구매 비용</t>
+        </is>
+      </c>
+      <c r="E1" s="12" t="inlineStr">
+        <is>
+          <t>별 비용 증가</t>
+        </is>
+      </c>
+      <c r="F1" s="12" t="inlineStr">
+        <is>
+          <t>효과 종류(0클릭/1달뎀/2달속도/3코인)</t>
+        </is>
+      </c>
+      <c r="G1" s="12" t="inlineStr">
+        <is>
+          <t>효과 수치</t>
+        </is>
+      </c>
+      <c r="H1" s="12" t="inlineStr">
+        <is>
+          <t>[참고] 완성까지 총 비용</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="13" t="inlineStr">
+        <is>
+          <t>index</t>
+        </is>
+      </c>
+      <c r="B2" s="13" t="inlineStr">
+        <is>
+          <t>starCount</t>
+        </is>
+      </c>
+      <c r="C2" s="13" t="inlineStr">
+        <is>
+          <t>unlockStage</t>
+        </is>
+      </c>
+      <c r="D2" s="13" t="inlineStr">
+        <is>
+          <t>starBaseCost</t>
+        </is>
+      </c>
+      <c r="E2" s="13" t="inlineStr">
+        <is>
+          <t>starCostIncrease</t>
+        </is>
+      </c>
+      <c r="F2" s="13" t="inlineStr">
+        <is>
+          <t>effectType</t>
+        </is>
+      </c>
+      <c r="G2" s="13" t="inlineStr">
+        <is>
+          <t>effectValue</t>
+        </is>
+      </c>
+      <c r="H2" s="13" t="inlineStr">
+        <is>
+          <t>previewTotalCost</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="B3" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="C3" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" s="14" t="n">
+        <v>200</v>
+      </c>
+      <c r="E3" s="14" t="n">
+        <v>50</v>
+      </c>
+      <c r="F3" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" s="14" t="n">
+        <v>30</v>
+      </c>
+      <c r="H3" s="15">
+        <f>B3*D3+E3*((B3-1)*B3/2)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="B4" s="14" t="n">
+        <v>10</v>
+      </c>
+      <c r="C4" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="D4" s="14" t="n">
+        <v>400</v>
+      </c>
+      <c r="E4" s="14" t="n">
+        <v>80</v>
+      </c>
+      <c r="F4" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="G4" s="14" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H4" s="15">
+        <f>B4*D4+E4*((B4-1)*B4/2)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="B5" s="14" t="n">
+        <v>6</v>
+      </c>
+      <c r="C5" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="D5" s="14" t="n">
+        <v>700</v>
+      </c>
+      <c r="E5" s="14" t="n">
+        <v>120</v>
+      </c>
+      <c r="F5" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" s="14" t="n">
+        <v>40</v>
+      </c>
+      <c r="H5" s="15">
+        <f>B5*D5+E5*((B5-1)*B5/2)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="B6" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="C6" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="D6" s="14" t="n">
+        <v>1200</v>
+      </c>
+      <c r="E6" s="14" t="n">
+        <v>200</v>
+      </c>
+      <c r="F6" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="14" t="n">
+        <v>80</v>
+      </c>
+      <c r="H6" s="15">
+        <f>B6*D6+E6*((B6-1)*B6/2)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="B7" s="14" t="n">
+        <v>9</v>
+      </c>
+      <c r="C7" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="D7" s="14" t="n">
+        <v>2000</v>
+      </c>
+      <c r="E7" s="14" t="n">
+        <v>300</v>
+      </c>
+      <c r="F7" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="G7" s="14" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H7" s="15">
+        <f>B7*D7+E7*((B7-1)*B7/2)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="B8" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="C8" s="14" t="n">
+        <v>6</v>
+      </c>
+      <c r="D8" s="14" t="n">
+        <v>3500</v>
+      </c>
+      <c r="E8" s="14" t="n">
+        <v>500</v>
+      </c>
+      <c r="F8" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="G8" s="14" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="H8" s="15">
+        <f>B8*D8+E8*((B8-1)*B8/2)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="14" t="n">
+        <v>6</v>
+      </c>
+      <c r="B9" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="C9" s="14" t="n">
+        <v>7</v>
+      </c>
+      <c r="D9" s="14" t="n">
+        <v>6000</v>
+      </c>
+      <c r="E9" s="14" t="n">
+        <v>800</v>
+      </c>
+      <c r="F9" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" s="14" t="n">
+        <v>150</v>
+      </c>
+      <c r="H9" s="15">
+        <f>B9*D9+E9*((B9-1)*B9/2)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="14" t="n">
+        <v>7</v>
+      </c>
+      <c r="B10" s="14" t="n">
+        <v>9</v>
+      </c>
+      <c r="C10" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="D10" s="14" t="n">
+        <v>10000</v>
+      </c>
+      <c r="E10" s="14" t="n">
+        <v>1500</v>
+      </c>
+      <c r="F10" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="14" t="n">
+        <v>250</v>
+      </c>
+      <c r="H10" s="15">
+        <f>B10*D10+E10*((B10-1)*B10/2)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="B11" s="14" t="n">
+        <v>9</v>
+      </c>
+      <c r="C11" s="14" t="n">
+        <v>9</v>
+      </c>
+      <c r="D11" s="14" t="n">
+        <v>17000</v>
+      </c>
+      <c r="E11" s="14" t="n">
+        <v>2500</v>
+      </c>
+      <c r="F11" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="G11" s="14" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H11" s="15">
+        <f>B11*D11+E11*((B11-1)*B11/2)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="14" t="n">
+        <v>9</v>
+      </c>
+      <c r="B12" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="C12" s="14" t="n">
+        <v>10</v>
+      </c>
+      <c r="D12" s="14" t="n">
+        <v>28000</v>
+      </c>
+      <c r="E12" s="14" t="n">
+        <v>4000</v>
+      </c>
+      <c r="F12" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="G12" s="14" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H12" s="15">
+        <f>B12*D12+E12*((B12-1)*B12/2)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="14" t="n">
+        <v>10</v>
+      </c>
+      <c r="B13" s="14" t="n">
+        <v>12</v>
+      </c>
+      <c r="C13" s="14" t="n">
+        <v>11</v>
+      </c>
+      <c r="D13" s="14" t="n">
+        <v>45000</v>
+      </c>
+      <c r="E13" s="14" t="n">
+        <v>6000</v>
+      </c>
+      <c r="F13" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G13" s="14" t="n">
+        <v>600</v>
+      </c>
+      <c r="H13" s="15">
+        <f>B13*D13+E13*((B13-1)*B13/2)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="14" t="n">
+        <v>11</v>
+      </c>
+      <c r="B14" s="14" t="n">
+        <v>7</v>
+      </c>
+      <c r="C14" s="14" t="n">
+        <v>12</v>
+      </c>
+      <c r="D14" s="14" t="n">
+        <v>75000</v>
+      </c>
+      <c r="E14" s="14" t="n">
+        <v>10000</v>
+      </c>
+      <c r="F14" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" s="14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H14" s="15">
+        <f>B14*D14+E14*((B14-1)*B14/2)</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:C6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>

--- a/DataTable/내일할래_데이터테이블.xlsx
+++ b/DataTable/내일할래_데이터테이블.xlsx
@@ -2,9 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Info" sheetId="1" state="visible" r:id="rId1"/>
@@ -16,16 +15,16 @@
     <sheet name="Balance" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="7">
+  <fonts count="8">
     <font>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
@@ -33,33 +32,50 @@
     </font>
     <font>
       <name val="맑은 고딕"/>
+      <charset val="129"/>
+      <family val="3"/>
       <b val="1"/>
       <sz val="16"/>
     </font>
     <font>
       <name val="맑은 고딕"/>
+      <charset val="129"/>
+      <family val="3"/>
       <i val="1"/>
-      <color rgb="00808080"/>
+      <color rgb="FF808080"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="맑은 고딕"/>
+      <charset val="129"/>
+      <family val="3"/>
       <b val="1"/>
       <sz val="11"/>
     </font>
     <font>
       <name val="맑은 고딕"/>
+      <charset val="129"/>
+      <family val="3"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="맑은 고딕"/>
+      <charset val="129"/>
+      <family val="3"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <color rgb="FFFFFFFF"/>
       <sz val="12"/>
     </font>
     <font>
       <name val="Consolas"/>
       <sz val="10"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <charset val="129"/>
+      <family val="3"/>
+      <sz val="8"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="7">
@@ -71,27 +87,27 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F2F2F2"/>
+        <fgColor rgb="FFF2F2F2"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
+        <fgColor rgb="FFFFF2CC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="004472C4"/>
+        <fgColor rgb="FF4472C4"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D9E1F2"/>
+        <fgColor rgb="FFD9E1F2"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E2EFDA"/>
+        <fgColor rgb="FFE2EFDA"/>
       </patternFill>
     </fill>
   </fills>
@@ -105,23 +121,24 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="00BFBFBF"/>
+        <color rgb="FFBFBFBF"/>
       </left>
       <right style="thin">
-        <color rgb="00BFBFBF"/>
+        <color rgb="FFBFBFBF"/>
       </right>
       <top style="thin">
-        <color rgb="00BFBFBF"/>
+        <color rgb="FFBFBFBF"/>
       </top>
       <bottom style="thin">
-        <color rgb="00BFBFBF"/>
+        <color rgb="FFBFBFBF"/>
       </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -131,7 +148,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -150,9 +166,12 @@
     <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -516,15 +535,15 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="B1:D43"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
-    <col width="3" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="62" customWidth="1" min="4" max="4"/>
+    <col width="3" customWidth="1" style="16" min="1" max="1"/>
+    <col width="26" customWidth="1" style="16" min="2" max="2"/>
+    <col width="30" customWidth="1" style="16" min="3" max="3"/>
+    <col width="62" customWidth="1" style="16" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="26.25" customHeight="1" s="16">
       <c r="B1" s="1" t="inlineStr">
         <is>
           <t>내일할래 — 밸런스 데이터 테이블</t>
@@ -532,7 +551,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="17" t="inlineStr">
         <is>
           <t>이 파일에서 수치를 고치고 CSV로 내보내면 게임에 바로 반영됩니다.</t>
         </is>
@@ -564,7 +583,7 @@
         </is>
       </c>
     </row>
-    <row r="6">
+    <row r="6" ht="40.5" customHeight="1" s="16">
       <c r="B6" s="5" t="inlineStr">
         <is>
           <t>2단계</t>
@@ -582,7 +601,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="5" t="inlineStr"/>
+      <c r="B7" s="5" t="n"/>
       <c r="C7" s="5" t="inlineStr">
         <is>
           <t>저장 위치</t>
@@ -612,7 +631,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="7" t="inlineStr">
+      <c r="B10" s="15" t="inlineStr">
         <is>
           <t>⚠ 엑셀은 '현재 열려 있는 시트 1개'만 CSV로 저장합니다. 시트를 4개 모두 반영하려면 시트마다 따로 저장해야 합니다.</t>
         </is>
@@ -627,120 +646,120 @@
       <c r="C12" s="4" t="n"/>
       <c r="D12" s="4" t="n"/>
     </row>
-    <row r="13">
-      <c r="B13" s="8" t="inlineStr">
+    <row r="13" ht="17.25" customHeight="1" s="16">
+      <c r="B13" s="7" t="inlineStr">
         <is>
           <t>시트</t>
         </is>
       </c>
-      <c r="C13" s="8" t="inlineStr">
+      <c r="C13" s="7" t="inlineStr">
         <is>
           <t>내보낼 CSV 파일</t>
         </is>
       </c>
-      <c r="D13" s="8" t="inlineStr">
+      <c r="D13" s="7" t="inlineStr">
         <is>
           <t>내용</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="9" t="inlineStr">
+      <c r="B14" s="8" t="inlineStr">
         <is>
           <t>Stage</t>
         </is>
       </c>
-      <c r="C14" s="10" t="inlineStr">
+      <c r="C14" s="9" t="inlineStr">
         <is>
           <t>Stage.csv</t>
         </is>
       </c>
-      <c r="D14" s="11" t="inlineStr">
+      <c r="D14" s="10" t="inlineStr">
         <is>
           <t>스테이지별 보스 체력 / 보스 처치 보상</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="B15" s="9" t="inlineStr">
+      <c r="B15" s="8" t="inlineStr">
         <is>
           <t>Monster</t>
         </is>
       </c>
-      <c r="C15" s="10" t="inlineStr">
+      <c r="C15" s="9" t="inlineStr">
         <is>
           <t>Monster.csv</t>
         </is>
       </c>
-      <c r="D15" s="11" t="inlineStr">
+      <c r="D15" s="10" t="inlineStr">
         <is>
           <t>스테이지별 일반 몬스터 종류마다의 체력 / 처치 보상</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="B16" s="9" t="inlineStr">
+      <c r="B16" s="8" t="inlineStr">
         <is>
           <t>Character</t>
         </is>
       </c>
-      <c r="C16" s="10" t="inlineStr">
+      <c r="C16" s="9" t="inlineStr">
         <is>
           <t>Character.csv</t>
         </is>
       </c>
-      <c r="D16" s="11" t="inlineStr">
+      <c r="D16" s="10" t="inlineStr">
         <is>
           <t>캐릭터 해금 비용, 터치(클릭) 공격력, 레벨업 비용</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="B17" s="9" t="inlineStr">
+      <c r="B17" s="8" t="inlineStr">
         <is>
           <t>Story</t>
         </is>
       </c>
-      <c r="C17" s="10" t="inlineStr">
+      <c r="C17" s="9" t="inlineStr">
         <is>
           <t>Story.csv</t>
         </is>
       </c>
-      <c r="D17" s="11" t="inlineStr">
+      <c r="D17" s="10" t="inlineStr">
         <is>
           <t>캐릭터 이야기 구매 비용, 필요 레벨, 달 자동공격 영구 강화량</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="B18" s="9" t="inlineStr">
+      <c r="B18" s="8" t="inlineStr">
         <is>
           <t>Constellation</t>
         </is>
       </c>
-      <c r="C18" s="10" t="inlineStr">
+      <c r="C18" s="9" t="inlineStr">
         <is>
           <t>Constellation.csv</t>
         </is>
       </c>
-      <c r="D18" s="11" t="inlineStr">
+      <c r="D18" s="10" t="inlineStr">
         <is>
           <t>별자리 구성 별 개수, 해금 스테이지, 별 구매 비용, 완성 효과</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="B19" s="9" t="inlineStr">
+      <c r="B19" s="8" t="inlineStr">
         <is>
           <t>Balance</t>
         </is>
       </c>
-      <c r="C19" s="10" t="inlineStr">
+      <c r="C19" s="9" t="inlineStr">
         <is>
           <t>Balance.csv</t>
         </is>
       </c>
-      <c r="D19" s="11" t="inlineStr">
+      <c r="D19" s="10" t="inlineStr">
         <is>
           <t>달 자동공격 기본 데미지·주기, 보스전 제한시간, 보스 도전 조건</t>
         </is>
@@ -773,7 +792,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="B23" s="5" t="inlineStr"/>
+      <c r="B23" s="5" t="n"/>
       <c r="C23" s="5" t="inlineStr">
         <is>
           <t>실제 클릭 데미지</t>
@@ -820,7 +839,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="B26" s="5" t="inlineStr"/>
+      <c r="B26" s="5" t="n"/>
       <c r="C26" s="5" t="inlineStr">
         <is>
           <t>실제 주기</t>
@@ -832,13 +851,13 @@
         </is>
       </c>
     </row>
-    <row r="27">
+    <row r="27" ht="27" customHeight="1" s="16">
       <c r="B27" s="5" t="inlineStr">
         <is>
           <t>이야기 해금</t>
         </is>
       </c>
-      <c r="C27" s="5" t="inlineStr"/>
+      <c r="C27" s="5" t="n"/>
       <c r="D27" s="6" t="inlineStr">
         <is>
           <t>그 이야기의 '캐릭터 번호'에 해당하는 캐릭터가 '필요 레벨' 이상이면 열림. 열린 뒤 꿈코인으로 구매하면 달이 영구 강화됨</t>
@@ -851,7 +870,7 @@
           <t>보스 도전 조건</t>
         </is>
       </c>
-      <c r="C28" s="5" t="inlineStr"/>
+      <c r="C28" s="5" t="n"/>
       <c r="D28" s="6" t="inlineStr">
         <is>
           <t>일반 몬스터를 killsRequired 마리 처치하면 보스 버튼이 열림</t>
@@ -864,7 +883,7 @@
           <t>보스전 제한시간</t>
         </is>
       </c>
-      <c r="C29" s="5" t="inlineStr"/>
+      <c r="C29" s="5" t="n"/>
       <c r="D29" s="6" t="inlineStr">
         <is>
           <t>bossDuration 초 안에 보스를 처치해야 다음 스테이지로 이동</t>
@@ -877,7 +896,7 @@
           <t>별자리 해금</t>
         </is>
       </c>
-      <c r="C30" s="5" t="inlineStr"/>
+      <c r="C30" s="5" t="n"/>
       <c r="D30" s="6" t="inlineStr">
         <is>
           <t>현재 스테이지가 '해금 스테이지' 이상이면 그 별자리의 별을 살 수 있음</t>
@@ -907,14 +926,14 @@
           <t>별자리 완성</t>
         </is>
       </c>
-      <c r="C32" s="5" t="inlineStr"/>
+      <c r="C32" s="5" t="n"/>
       <c r="D32" s="6" t="inlineStr">
         <is>
           <t>구성 별을 전부 사면 완성 → 효과 발동 + 배경에 별자리 리소스 배치</t>
         </is>
       </c>
     </row>
-    <row r="33">
+    <row r="33" ht="27" customHeight="1" s="16">
       <c r="B33" s="5" t="inlineStr">
         <is>
           <t>별자리 효과 종류</t>
@@ -932,7 +951,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="B35" s="2" t="inlineStr">
+      <c r="B35" s="17" t="inlineStr">
         <is>
           <t>Character 시트의 [참고] 컬럼은 위 계산식을 미리 계산해 보여주는 것으로, 게임은 이 값을 읽지 않습니다.</t>
         </is>
@@ -947,7 +966,7 @@
       <c r="C37" s="4" t="n"/>
       <c r="D37" s="4" t="n"/>
     </row>
-    <row r="38">
+    <row r="38" ht="27" customHeight="1" s="16">
       <c r="B38" s="5" t="inlineStr">
         <is>
           <t>2행 = 영문 키</t>
@@ -964,7 +983,7 @@
         </is>
       </c>
     </row>
-    <row r="39">
+    <row r="39" ht="27" customHeight="1" s="16">
       <c r="B39" s="5" t="inlineStr">
         <is>
           <t>1행 = 한글 제목</t>
@@ -1015,7 +1034,7 @@
         </is>
       </c>
     </row>
-    <row r="42">
+    <row r="42" ht="27" customHeight="1" s="16">
       <c r="B42" s="5" t="inlineStr">
         <is>
           <t>없는 항목</t>
@@ -1064,68 +1083,187 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:C15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" style="16" min="1" max="3"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="12" t="inlineStr">
+    <row r="1" ht="30" customHeight="1" s="16">
+      <c r="A1" s="11" t="inlineStr">
         <is>
           <t>#스테이지 번호</t>
         </is>
       </c>
-      <c r="B1" s="12" t="inlineStr">
+      <c r="B1" s="11" t="inlineStr">
         <is>
           <t>보스 체력</t>
         </is>
       </c>
-      <c r="C1" s="12" t="inlineStr">
+      <c r="C1" s="11" t="inlineStr">
         <is>
           <t>보스 처치 보상(꿈코인)</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="13" t="inlineStr">
+    <row r="2" ht="17.25" customHeight="1" s="16">
+      <c r="A2" s="12" t="inlineStr">
         <is>
           <t>stage</t>
         </is>
       </c>
-      <c r="B2" s="13" t="inlineStr">
+      <c r="B2" s="12" t="inlineStr">
         <is>
           <t>bossHp</t>
         </is>
       </c>
-      <c r="C2" s="13" t="inlineStr">
+      <c r="C2" s="12" t="inlineStr">
         <is>
           <t>bossCoinReward</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="14" t="n">
+      <c r="A3" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="B3" s="14" t="n">
-        <v>500</v>
-      </c>
-      <c r="C3" s="14" t="n">
+      <c r="B3" s="13" t="n">
+        <v>1788</v>
+      </c>
+      <c r="C3" s="13" t="n">
         <v>50</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="14" t="n">
+      <c r="A4" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="B4" s="14" t="n">
-        <v>900</v>
-      </c>
-      <c r="C4" s="14" t="n">
-        <v>80</v>
+      <c r="B4" s="13" t="n">
+        <v>3895</v>
+      </c>
+      <c r="C4" s="13" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="B5" s="13" t="n">
+        <v>6868</v>
+      </c>
+      <c r="C5" s="13" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="B6" s="13" t="n">
+        <v>12921</v>
+      </c>
+      <c r="C6" s="13" t="n">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="B7" s="13" t="n">
+        <v>32037</v>
+      </c>
+      <c r="C7" s="13" t="n">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="B8" s="13" t="n">
+        <v>88506</v>
+      </c>
+      <c r="C8" s="13" t="n">
+        <v>1700</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="B9" s="13" t="n">
+        <v>257034</v>
+      </c>
+      <c r="C9" s="13" t="n">
+        <v>4650</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="13" t="n">
+        <v>7</v>
+      </c>
+      <c r="B10" s="13" t="n">
+        <v>852309</v>
+      </c>
+      <c r="C10" s="13" t="n">
+        <v>14050</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="13" t="n">
+        <v>8</v>
+      </c>
+      <c r="B11" s="13" t="n">
+        <v>1855963</v>
+      </c>
+      <c r="C11" s="13" t="n">
+        <v>35750</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="13" t="n">
+        <v>9</v>
+      </c>
+      <c r="B12" s="13" t="n">
+        <v>3735088</v>
+      </c>
+      <c r="C12" s="13" t="n">
+        <v>72600</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="13" t="n">
+        <v>10</v>
+      </c>
+      <c r="B13" s="13" t="n">
+        <v>4465671</v>
+      </c>
+      <c r="C13" s="13" t="n">
+        <v>135250</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="13" t="n">
+        <v>11</v>
+      </c>
+      <c r="B14" s="13" t="n">
+        <v>4210851</v>
+      </c>
+      <c r="C14" s="13" t="n">
+        <v>227900</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B15" s="13" t="n">
+        <v>5743061</v>
+      </c>
+      <c r="C15" s="13" t="n">
+        <v>312350</v>
       </c>
     </row>
   </sheetData>
@@ -1139,113 +1277,418 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:D28"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" style="16" min="1" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="12" t="inlineStr">
+    <row r="1" ht="30" customHeight="1" s="16">
+      <c r="A1" s="11" t="inlineStr">
         <is>
           <t>#스테이지 번호</t>
         </is>
       </c>
-      <c r="B1" s="12" t="inlineStr">
+      <c r="B1" s="11" t="inlineStr">
         <is>
           <t>몬스터 순번</t>
         </is>
       </c>
-      <c r="C1" s="12" t="inlineStr">
+      <c r="C1" s="11" t="inlineStr">
         <is>
           <t>몬스터 체력</t>
         </is>
       </c>
-      <c r="D1" s="12" t="inlineStr">
+      <c r="D1" s="11" t="inlineStr">
         <is>
           <t>처치 보상(꿈코인)</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="13" t="inlineStr">
+    <row r="2" ht="17.25" customHeight="1" s="16">
+      <c r="A2" s="12" t="inlineStr">
         <is>
           <t>stage</t>
         </is>
       </c>
-      <c r="B2" s="13" t="inlineStr">
+      <c r="B2" s="12" t="inlineStr">
         <is>
           <t>index</t>
         </is>
       </c>
-      <c r="C2" s="13" t="inlineStr">
+      <c r="C2" s="12" t="inlineStr">
         <is>
           <t>hp</t>
         </is>
       </c>
-      <c r="D2" s="13" t="inlineStr">
+      <c r="D2" s="12" t="inlineStr">
         <is>
           <t>coinReward</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="14" t="n">
+      <c r="A3" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="B3" s="14" t="n">
+      <c r="B3" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="C3" s="14" t="n">
-        <v>100</v>
-      </c>
-      <c r="D3" s="14" t="n">
+      <c r="C3" s="13" t="n">
+        <v>148</v>
+      </c>
+      <c r="D3" s="13" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="14" t="n">
+      <c r="A4" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="B4" s="14" t="n">
+      <c r="B4" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="C4" s="14" t="n">
-        <v>120</v>
-      </c>
-      <c r="D4" s="14" t="n">
+      <c r="C4" s="13" t="n">
+        <v>182</v>
+      </c>
+      <c r="D4" s="13" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="14" t="n">
+      <c r="A5" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="B5" s="14" t="n">
+      <c r="B5" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="C5" s="14" t="n">
-        <v>300</v>
-      </c>
-      <c r="D5" s="14" t="n">
+      <c r="C5" s="13" t="n">
+        <v>270</v>
+      </c>
+      <c r="D5" s="13" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="B6" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" s="13" t="n">
+        <v>330</v>
+      </c>
+      <c r="D6" s="13" t="n">
         <v>3</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="14" t="n">
+    <row r="7">
+      <c r="A7" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="B7" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" s="13" t="n">
+        <v>513</v>
+      </c>
+      <c r="D7" s="13" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="B8" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="B6" s="14" t="n">
+      <c r="C8" s="13" t="n">
+        <v>627</v>
+      </c>
+      <c r="D8" s="13" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="B9" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" s="13" t="n">
+        <v>918</v>
+      </c>
+      <c r="D9" s="13" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="B10" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="C6" s="14" t="n">
-        <v>350</v>
-      </c>
-      <c r="D6" s="14" t="n">
-        <v>3</v>
+      <c r="C10" s="13" t="n">
+        <v>1122</v>
+      </c>
+      <c r="D10" s="13" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="B11" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" s="13" t="n">
+        <v>1958</v>
+      </c>
+      <c r="D11" s="13" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="B12" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" s="13" t="n">
+        <v>2392</v>
+      </c>
+      <c r="D12" s="13" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="B13" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" s="13" t="n">
+        <v>4280</v>
+      </c>
+      <c r="D13" s="13" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="B14" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="C14" s="13" t="n">
+        <v>5230</v>
+      </c>
+      <c r="D14" s="13" t="n">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="B15" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" s="13" t="n">
+        <v>11624</v>
+      </c>
+      <c r="D15" s="13" t="n">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="B16" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="C16" s="13" t="n">
+        <v>14207</v>
+      </c>
+      <c r="D16" s="13" t="n">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="13" t="n">
+        <v>7</v>
+      </c>
+      <c r="B17" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" s="13" t="n">
+        <v>35154</v>
+      </c>
+      <c r="D17" s="13" t="n">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="13" t="n">
+        <v>7</v>
+      </c>
+      <c r="B18" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="C18" s="13" t="n">
+        <v>42966</v>
+      </c>
+      <c r="D18" s="13" t="n">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="13" t="n">
+        <v>8</v>
+      </c>
+      <c r="B19" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="C19" s="13" t="n">
+        <v>89356</v>
+      </c>
+      <c r="D19" s="13" t="n">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="13" t="n">
+        <v>8</v>
+      </c>
+      <c r="B20" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="C20" s="13" t="n">
+        <v>109214</v>
+      </c>
+      <c r="D20" s="13" t="n">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="13" t="n">
+        <v>9</v>
+      </c>
+      <c r="B21" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="C21" s="13" t="n">
+        <v>181453</v>
+      </c>
+      <c r="D21" s="13" t="n">
+        <v>1452</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="13" t="n">
+        <v>9</v>
+      </c>
+      <c r="B22" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="C22" s="13" t="n">
+        <v>221775</v>
+      </c>
+      <c r="D22" s="13" t="n">
+        <v>1774</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="13" t="n">
+        <v>10</v>
+      </c>
+      <c r="B23" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="C23" s="13" t="n">
+        <v>338099</v>
+      </c>
+      <c r="D23" s="13" t="n">
+        <v>2705</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="13" t="n">
+        <v>10</v>
+      </c>
+      <c r="B24" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="C24" s="13" t="n">
+        <v>413233</v>
+      </c>
+      <c r="D24" s="13" t="n">
+        <v>3306</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="13" t="n">
+        <v>11</v>
+      </c>
+      <c r="B25" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="C25" s="13" t="n">
+        <v>569765</v>
+      </c>
+      <c r="D25" s="13" t="n">
+        <v>4558</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="13" t="n">
+        <v>11</v>
+      </c>
+      <c r="B26" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="C26" s="13" t="n">
+        <v>696379</v>
+      </c>
+      <c r="D26" s="13" t="n">
+        <v>5571</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B27" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="C27" s="13" t="n">
+        <v>780860</v>
+      </c>
+      <c r="D27" s="13" t="n">
+        <v>6247</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B28" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="C28" s="13" t="n">
+        <v>954384</v>
+      </c>
+      <c r="D28" s="13" t="n">
+        <v>7635</v>
       </c>
     </row>
   </sheetData>
@@ -1259,204 +1702,351 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I5"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:I10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
-    <col width="20" customWidth="1" min="8" max="8"/>
-    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" style="16" min="1" max="9"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="12" t="inlineStr">
+    <row r="1" ht="30" customHeight="1" s="16">
+      <c r="A1" s="11" t="inlineStr">
         <is>
           <t>#캐릭터 번호</t>
         </is>
       </c>
-      <c r="B1" s="12" t="inlineStr">
+      <c r="B1" s="11" t="inlineStr">
         <is>
           <t>해금 비용(꿈코인)</t>
         </is>
       </c>
-      <c r="C1" s="12" t="inlineStr">
+      <c r="C1" s="11" t="inlineStr">
         <is>
           <t>기본 데미지(LV1)</t>
         </is>
       </c>
-      <c r="D1" s="12" t="inlineStr">
+      <c r="D1" s="11" t="inlineStr">
         <is>
           <t>레벨당 데미지 증가</t>
         </is>
       </c>
-      <c r="E1" s="12" t="inlineStr">
+      <c r="E1" s="11" t="inlineStr">
         <is>
           <t>최대 레벨</t>
         </is>
       </c>
-      <c r="F1" s="12" t="inlineStr">
+      <c r="F1" s="11" t="inlineStr">
         <is>
           <t>레벨업 기본 비용</t>
         </is>
       </c>
-      <c r="G1" s="12" t="inlineStr">
+      <c r="G1" s="11" t="inlineStr">
         <is>
           <t>레벨업 비용 증가/레벨</t>
         </is>
       </c>
-      <c r="H1" s="12" t="inlineStr">
+      <c r="H1" s="11" t="inlineStr">
         <is>
           <t>[참고] 최대레벨 데미지</t>
         </is>
       </c>
-      <c r="I1" s="12" t="inlineStr">
+      <c r="I1" s="11" t="inlineStr">
         <is>
           <t>[참고] 만렙까지 총 강화비용</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="13" t="inlineStr">
+    <row r="2" ht="17.25" customHeight="1" s="16">
+      <c r="A2" s="12" t="inlineStr">
         <is>
           <t>index</t>
         </is>
       </c>
-      <c r="B2" s="13" t="inlineStr">
+      <c r="B2" s="12" t="inlineStr">
         <is>
           <t>unlockCost</t>
         </is>
       </c>
-      <c r="C2" s="13" t="inlineStr">
+      <c r="C2" s="12" t="inlineStr">
         <is>
           <t>baseDamage</t>
         </is>
       </c>
-      <c r="D2" s="13" t="inlineStr">
+      <c r="D2" s="12" t="inlineStr">
         <is>
           <t>damagePerLevel</t>
         </is>
       </c>
-      <c r="E2" s="13" t="inlineStr">
+      <c r="E2" s="12" t="inlineStr">
         <is>
           <t>maxLevel</t>
         </is>
       </c>
-      <c r="F2" s="13" t="inlineStr">
+      <c r="F2" s="12" t="inlineStr">
         <is>
           <t>levelUpBaseCost</t>
         </is>
       </c>
-      <c r="G2" s="13" t="inlineStr">
+      <c r="G2" s="12" t="inlineStr">
         <is>
           <t>levelUpCostPerLevel</t>
         </is>
       </c>
-      <c r="H2" s="13" t="inlineStr">
+      <c r="H2" s="12" t="inlineStr">
         <is>
           <t>previewMaxDamage</t>
         </is>
       </c>
-      <c r="I2" s="13" t="inlineStr">
+      <c r="I2" s="12" t="inlineStr">
         <is>
           <t>previewTotalCost</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="14" t="n">
+      <c r="A3" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="B3" s="14" t="n">
+      <c r="B3" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="C3" s="14" t="n">
+      <c r="C3" s="13" t="n">
         <v>10</v>
       </c>
-      <c r="D3" s="14" t="n">
-        <v>2</v>
-      </c>
-      <c r="E3" s="14" t="n">
+      <c r="D3" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="E3" s="13" t="n">
         <v>200</v>
       </c>
-      <c r="F3" s="14" t="n">
+      <c r="F3" s="13" t="n">
         <v>50</v>
       </c>
-      <c r="G3" s="14" t="n">
-        <v>10</v>
-      </c>
-      <c r="H3" s="15">
+      <c r="G3" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="H3" s="14">
         <f>C3+(E3-1)*D3</f>
         <v/>
       </c>
-      <c r="I3" s="15">
+      <c r="I3" s="14">
         <f>(E3-1)*F3+G3*((E3-2)*(E3-1)/2)</f>
         <v/>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="14" t="n">
+      <c r="A4" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="B4" s="14" t="n">
-        <v>100</v>
-      </c>
-      <c r="C4" s="14" t="n">
+      <c r="B4" s="13" t="n">
+        <v>800</v>
+      </c>
+      <c r="C4" s="13" t="n">
+        <v>16</v>
+      </c>
+      <c r="D4" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="D4" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="E4" s="14" t="n">
+      <c r="E4" s="13" t="n">
         <v>200</v>
       </c>
-      <c r="F4" s="14" t="n">
-        <v>40</v>
-      </c>
-      <c r="G4" s="14" t="n">
+      <c r="F4" s="13" t="n">
+        <v>80</v>
+      </c>
+      <c r="G4" s="13" t="n">
         <v>8</v>
       </c>
-      <c r="H4" s="15">
+      <c r="H4" s="14">
         <f>C4+(E4-1)*D4</f>
         <v/>
       </c>
-      <c r="I4" s="15">
+      <c r="I4" s="14">
         <f>(E4-1)*F4+G4*((E4-2)*(E4-1)/2)</f>
         <v/>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="14" t="n">
+      <c r="A5" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="B5" s="14" t="n">
-        <v>300</v>
-      </c>
-      <c r="C5" s="14" t="n">
+      <c r="B5" s="13" t="n">
+        <v>1280</v>
+      </c>
+      <c r="C5" s="13" t="n">
+        <v>26</v>
+      </c>
+      <c r="D5" s="13" t="n">
         <v>8</v>
       </c>
-      <c r="D5" s="14" t="n">
-        <v>2</v>
-      </c>
-      <c r="E5" s="14" t="n">
+      <c r="E5" s="13" t="n">
         <v>200</v>
       </c>
-      <c r="F5" s="14" t="n">
-        <v>60</v>
-      </c>
-      <c r="G5" s="14" t="n">
-        <v>12</v>
-      </c>
-      <c r="H5" s="15">
+      <c r="F5" s="13" t="n">
+        <v>128</v>
+      </c>
+      <c r="G5" s="13" t="n">
+        <v>13</v>
+      </c>
+      <c r="H5" s="14">
         <f>C5+(E5-1)*D5</f>
         <v/>
       </c>
-      <c r="I5" s="15">
+      <c r="I5" s="14">
         <f>(E5-1)*F5+G5*((E5-2)*(E5-1)/2)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="B6" s="13" t="n">
+        <v>2048</v>
+      </c>
+      <c r="C6" s="13" t="n">
+        <v>41</v>
+      </c>
+      <c r="D6" s="13" t="n">
+        <v>12</v>
+      </c>
+      <c r="E6" s="13" t="n">
+        <v>200</v>
+      </c>
+      <c r="F6" s="13" t="n">
+        <v>205</v>
+      </c>
+      <c r="G6" s="13" t="n">
+        <v>20</v>
+      </c>
+      <c r="H6">
+        <f>C6+(E6-1)*D6</f>
+        <v/>
+      </c>
+      <c r="I6">
+        <f>(E6-1)*F6+G6*((E6-2)*(E6-1)/2)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="B7" s="13" t="n">
+        <v>3277</v>
+      </c>
+      <c r="C7" s="13" t="n">
+        <v>66</v>
+      </c>
+      <c r="D7" s="13" t="n">
+        <v>20</v>
+      </c>
+      <c r="E7" s="13" t="n">
+        <v>200</v>
+      </c>
+      <c r="F7" s="13" t="n">
+        <v>328</v>
+      </c>
+      <c r="G7" s="13" t="n">
+        <v>33</v>
+      </c>
+      <c r="H7">
+        <f>C7+(E7-1)*D7</f>
+        <v/>
+      </c>
+      <c r="I7">
+        <f>(E7-1)*F7+G7*((E7-2)*(E7-1)/2)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="B8" s="13" t="n">
+        <v>5243</v>
+      </c>
+      <c r="C8" s="13" t="n">
+        <v>105</v>
+      </c>
+      <c r="D8" s="13" t="n">
+        <v>31</v>
+      </c>
+      <c r="E8" s="13" t="n">
+        <v>200</v>
+      </c>
+      <c r="F8" s="13" t="n">
+        <v>524</v>
+      </c>
+      <c r="G8" s="13" t="n">
+        <v>52</v>
+      </c>
+      <c r="H8">
+        <f>C8+(E8-1)*D8</f>
+        <v/>
+      </c>
+      <c r="I8">
+        <f>(E8-1)*F8+G8*((E8-2)*(E8-1)/2)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="B9" s="13" t="n">
+        <v>8389</v>
+      </c>
+      <c r="C9" s="13" t="n">
+        <v>168</v>
+      </c>
+      <c r="D9" s="13" t="n">
+        <v>50</v>
+      </c>
+      <c r="E9" s="13" t="n">
+        <v>200</v>
+      </c>
+      <c r="F9" s="13" t="n">
+        <v>839</v>
+      </c>
+      <c r="G9" s="13" t="n">
+        <v>84</v>
+      </c>
+      <c r="H9">
+        <f>C9+(E9-1)*D9</f>
+        <v/>
+      </c>
+      <c r="I9">
+        <f>(E9-1)*F9+G9*((E9-2)*(E9-1)/2)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="13" t="n">
+        <v>7</v>
+      </c>
+      <c r="B10" s="13" t="n">
+        <v>13422</v>
+      </c>
+      <c r="C10" s="13" t="n">
+        <v>268</v>
+      </c>
+      <c r="D10" s="13" t="n">
+        <v>81</v>
+      </c>
+      <c r="E10" s="13" t="n">
+        <v>200</v>
+      </c>
+      <c r="F10" s="13" t="n">
+        <v>1342</v>
+      </c>
+      <c r="G10" s="13" t="n">
+        <v>134</v>
+      </c>
+      <c r="H10">
+        <f>C10+(E10-1)*D10</f>
+        <v/>
+      </c>
+      <c r="I10">
+        <f>(E10-1)*F10+G10*((E10-2)*(E10-1)/2)</f>
         <v/>
       </c>
     </row>
@@ -1471,139 +2061,234 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:F10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" style="16" min="1" max="6"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="12" t="inlineStr">
+    <row r="1" ht="30" customHeight="1" s="16">
+      <c r="A1" s="11" t="inlineStr">
         <is>
           <t>#이야기 번호</t>
         </is>
       </c>
-      <c r="B1" s="12" t="inlineStr">
+      <c r="B1" s="11" t="inlineStr">
         <is>
           <t>캐릭터 번호</t>
         </is>
       </c>
-      <c r="C1" s="12" t="inlineStr">
+      <c r="C1" s="11" t="inlineStr">
         <is>
           <t>필요 레벨</t>
         </is>
       </c>
-      <c r="D1" s="12" t="inlineStr">
+      <c r="D1" s="11" t="inlineStr">
         <is>
           <t>구매 비용(꿈코인)</t>
         </is>
       </c>
-      <c r="E1" s="12" t="inlineStr">
+      <c r="E1" s="11" t="inlineStr">
         <is>
           <t>달 데미지 증가</t>
         </is>
       </c>
-      <c r="F1" s="12" t="inlineStr">
+      <c r="F1" s="11" t="inlineStr">
         <is>
           <t>달 주기 감소(초)</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="13" t="inlineStr">
+    <row r="2" ht="17.25" customHeight="1" s="16">
+      <c r="A2" s="12" t="inlineStr">
         <is>
           <t>index</t>
         </is>
       </c>
-      <c r="B2" s="13" t="inlineStr">
+      <c r="B2" s="12" t="inlineStr">
         <is>
           <t>characterIndex</t>
         </is>
       </c>
-      <c r="C2" s="13" t="inlineStr">
+      <c r="C2" s="12" t="inlineStr">
         <is>
           <t>requiredLevel</t>
         </is>
       </c>
-      <c r="D2" s="13" t="inlineStr">
+      <c r="D2" s="12" t="inlineStr">
         <is>
           <t>cost</t>
         </is>
       </c>
-      <c r="E2" s="13" t="inlineStr">
+      <c r="E2" s="12" t="inlineStr">
         <is>
           <t>moonDamageBonus</t>
         </is>
       </c>
-      <c r="F2" s="13" t="inlineStr">
+      <c r="F2" s="12" t="inlineStr">
         <is>
           <t>moonIntervalReduction</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="14" t="n">
+      <c r="A3" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="B3" s="14" t="n">
+      <c r="B3" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="C3" s="14" t="n">
-        <v>150</v>
-      </c>
-      <c r="D3" s="14" t="n">
-        <v>500</v>
-      </c>
-      <c r="E3" s="14" t="n">
+      <c r="C3" s="13" t="n">
+        <v>10</v>
+      </c>
+      <c r="D3" s="13" t="n">
+        <v>4200</v>
+      </c>
+      <c r="E3" s="13" t="n">
+        <v>300</v>
+      </c>
+      <c r="F3" s="13" t="n">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="B4" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" s="13" t="n">
         <v>20</v>
       </c>
-      <c r="F3" s="14" t="n">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="B4" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="C4" s="14" t="n">
-        <v>150</v>
-      </c>
-      <c r="D4" s="14" t="n">
-        <v>800</v>
-      </c>
-      <c r="E4" s="14" t="n">
+      <c r="D4" s="13" t="n">
+        <v>6720</v>
+      </c>
+      <c r="E4" s="13" t="n">
+        <v>480</v>
+      </c>
+      <c r="F4" s="13" t="n">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="B5" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="C5" s="13" t="n">
         <v>30</v>
       </c>
-      <c r="F4" s="14" t="n">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="14" t="n">
-        <v>2</v>
-      </c>
-      <c r="B5" s="14" t="n">
-        <v>2</v>
-      </c>
-      <c r="C5" s="14" t="n">
-        <v>150</v>
-      </c>
-      <c r="D5" s="14" t="n">
-        <v>1200</v>
-      </c>
-      <c r="E5" s="14" t="n">
+      <c r="D5" s="13" t="n">
+        <v>10752</v>
+      </c>
+      <c r="E5" s="13" t="n">
+        <v>768</v>
+      </c>
+      <c r="F5" s="13" t="n">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="B6" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="C6" s="13" t="n">
         <v>40</v>
       </c>
-      <c r="F5" s="14" t="n">
-        <v>0.1</v>
+      <c r="D6" s="13" t="n">
+        <v>17203</v>
+      </c>
+      <c r="E6" s="13" t="n">
+        <v>1229</v>
+      </c>
+      <c r="F6" s="13" t="n">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="B7" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="C7" s="13" t="n">
+        <v>50</v>
+      </c>
+      <c r="D7" s="13" t="n">
+        <v>27525</v>
+      </c>
+      <c r="E7" s="13" t="n">
+        <v>1966</v>
+      </c>
+      <c r="F7" s="13" t="n">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="B8" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="C8" s="13" t="n">
+        <v>60</v>
+      </c>
+      <c r="D8" s="13" t="n">
+        <v>44040</v>
+      </c>
+      <c r="E8" s="13" t="n">
+        <v>3146</v>
+      </c>
+      <c r="F8" s="13" t="n">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="B9" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="C9" s="13" t="n">
+        <v>70</v>
+      </c>
+      <c r="D9" s="13" t="n">
+        <v>70464</v>
+      </c>
+      <c r="E9" s="13" t="n">
+        <v>5033</v>
+      </c>
+      <c r="F9" s="13" t="n">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="13" t="n">
+        <v>7</v>
+      </c>
+      <c r="B10" s="13" t="n">
+        <v>7</v>
+      </c>
+      <c r="C10" s="13" t="n">
+        <v>80</v>
+      </c>
+      <c r="D10" s="13" t="n">
+        <v>112743</v>
+      </c>
+      <c r="E10" s="13" t="n">
+        <v>8053</v>
+      </c>
+      <c r="F10" s="13" t="n">
+        <v>0.06</v>
       </c>
     </row>
   </sheetData>
@@ -1618,422 +2303,415 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:H14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
-    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" style="16" min="1" max="8"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="12" t="inlineStr">
+    <row r="1" ht="30" customHeight="1" s="16">
+      <c r="A1" s="11" t="inlineStr">
         <is>
           <t>#별자리 번호</t>
         </is>
       </c>
-      <c r="B1" s="12" t="inlineStr">
+      <c r="B1" s="11" t="inlineStr">
         <is>
           <t>구성 별 개수</t>
         </is>
       </c>
-      <c r="C1" s="12" t="inlineStr">
+      <c r="C1" s="11" t="inlineStr">
         <is>
           <t>해금 스테이지</t>
         </is>
       </c>
-      <c r="D1" s="12" t="inlineStr">
+      <c r="D1" s="11" t="inlineStr">
         <is>
           <t>별 첫 구매 비용</t>
         </is>
       </c>
-      <c r="E1" s="12" t="inlineStr">
+      <c r="E1" s="11" t="inlineStr">
         <is>
           <t>별 비용 증가</t>
         </is>
       </c>
-      <c r="F1" s="12" t="inlineStr">
+      <c r="F1" s="11" t="inlineStr">
         <is>
           <t>효과 종류(0클릭/1달뎀/2달속도/3코인)</t>
         </is>
       </c>
-      <c r="G1" s="12" t="inlineStr">
+      <c r="G1" s="11" t="inlineStr">
         <is>
           <t>효과 수치</t>
         </is>
       </c>
-      <c r="H1" s="12" t="inlineStr">
+      <c r="H1" s="11" t="inlineStr">
         <is>
           <t>[참고] 완성까지 총 비용</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="13" t="inlineStr">
+    <row r="2" ht="17.25" customHeight="1" s="16">
+      <c r="A2" s="12" t="inlineStr">
         <is>
           <t>index</t>
         </is>
       </c>
-      <c r="B2" s="13" t="inlineStr">
+      <c r="B2" s="12" t="inlineStr">
         <is>
           <t>starCount</t>
         </is>
       </c>
-      <c r="C2" s="13" t="inlineStr">
+      <c r="C2" s="12" t="inlineStr">
         <is>
           <t>unlockStage</t>
         </is>
       </c>
-      <c r="D2" s="13" t="inlineStr">
+      <c r="D2" s="12" t="inlineStr">
         <is>
           <t>starBaseCost</t>
         </is>
       </c>
-      <c r="E2" s="13" t="inlineStr">
+      <c r="E2" s="12" t="inlineStr">
         <is>
           <t>starCostIncrease</t>
         </is>
       </c>
-      <c r="F2" s="13" t="inlineStr">
+      <c r="F2" s="12" t="inlineStr">
         <is>
           <t>effectType</t>
         </is>
       </c>
-      <c r="G2" s="13" t="inlineStr">
+      <c r="G2" s="12" t="inlineStr">
         <is>
           <t>effectValue</t>
         </is>
       </c>
-      <c r="H2" s="13" t="inlineStr">
+      <c r="H2" s="12" t="inlineStr">
         <is>
           <t>previewTotalCost</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="14" t="n">
+      <c r="A3" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="B3" s="14" t="n">
+      <c r="B3" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="C3" s="14" t="n">
+      <c r="C3" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="D3" s="14" t="n">
-        <v>200</v>
-      </c>
-      <c r="E3" s="14" t="n">
+      <c r="D3" s="13" t="n">
         <v>50</v>
       </c>
-      <c r="F3" s="14" t="n">
+      <c r="E3" s="13" t="n">
+        <v>10</v>
+      </c>
+      <c r="F3" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="G3" s="14" t="n">
-        <v>30</v>
-      </c>
-      <c r="H3" s="15">
+      <c r="G3" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="H3" s="14">
         <f>B3*D3+E3*((B3-1)*B3/2)</f>
         <v/>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="14" t="n">
+      <c r="A4" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="B4" s="14" t="n">
+      <c r="B4" s="13" t="n">
         <v>10</v>
       </c>
-      <c r="C4" s="14" t="n">
+      <c r="C4" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="D4" s="14" t="n">
-        <v>400</v>
-      </c>
-      <c r="E4" s="14" t="n">
-        <v>80</v>
-      </c>
-      <c r="F4" s="14" t="n">
+      <c r="D4" s="13" t="n">
+        <v>50</v>
+      </c>
+      <c r="E4" s="13" t="n">
+        <v>10</v>
+      </c>
+      <c r="F4" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="G4" s="14" t="n">
+      <c r="G4" s="13" t="n">
         <v>0.1</v>
       </c>
-      <c r="H4" s="15">
+      <c r="H4" s="14">
         <f>B4*D4+E4*((B4-1)*B4/2)</f>
         <v/>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="14" t="n">
+      <c r="A5" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="B5" s="14" t="n">
+      <c r="B5" s="13" t="n">
         <v>6</v>
       </c>
-      <c r="C5" s="14" t="n">
+      <c r="C5" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="D5" s="14" t="n">
-        <v>700</v>
-      </c>
-      <c r="E5" s="14" t="n">
-        <v>120</v>
-      </c>
-      <c r="F5" s="14" t="n">
+      <c r="D5" s="13" t="n">
+        <v>123</v>
+      </c>
+      <c r="E5" s="13" t="n">
+        <v>31</v>
+      </c>
+      <c r="F5" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="G5" s="14" t="n">
-        <v>40</v>
-      </c>
-      <c r="H5" s="15">
+      <c r="G5" s="13" t="n">
+        <v>8</v>
+      </c>
+      <c r="H5" s="14">
         <f>B5*D5+E5*((B5-1)*B5/2)</f>
         <v/>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="14" t="n">
+      <c r="A6" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="B6" s="14" t="n">
+      <c r="B6" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="C6" s="14" t="n">
+      <c r="C6" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="D6" s="14" t="n">
-        <v>1200</v>
-      </c>
-      <c r="E6" s="14" t="n">
-        <v>200</v>
-      </c>
-      <c r="F6" s="14" t="n">
+      <c r="D6" s="13" t="n">
+        <v>464</v>
+      </c>
+      <c r="E6" s="13" t="n">
+        <v>116</v>
+      </c>
+      <c r="F6" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="G6" s="14" t="n">
-        <v>80</v>
-      </c>
-      <c r="H6" s="15">
+      <c r="G6" s="13" t="n">
+        <v>12</v>
+      </c>
+      <c r="H6" s="14">
         <f>B6*D6+E6*((B6-1)*B6/2)</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="14" t="n">
+      <c r="A7" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="B7" s="14" t="n">
+      <c r="B7" s="13" t="n">
         <v>9</v>
       </c>
-      <c r="C7" s="14" t="n">
+      <c r="C7" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="D7" s="14" t="n">
-        <v>2000</v>
-      </c>
-      <c r="E7" s="14" t="n">
-        <v>300</v>
-      </c>
-      <c r="F7" s="14" t="n">
+      <c r="D7" s="13" t="n">
+        <v>317</v>
+      </c>
+      <c r="E7" s="13" t="n">
+        <v>79</v>
+      </c>
+      <c r="F7" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="G7" s="14" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="H7" s="15">
+      <c r="G7" s="13" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="H7" s="14">
         <f>B7*D7+E7*((B7-1)*B7/2)</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="14" t="n">
+      <c r="A8" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="B8" s="14" t="n">
+      <c r="B8" s="13" t="n">
         <v>8</v>
       </c>
-      <c r="C8" s="14" t="n">
+      <c r="C8" s="13" t="n">
         <v>6</v>
       </c>
-      <c r="D8" s="14" t="n">
-        <v>3500</v>
-      </c>
-      <c r="E8" s="14" t="n">
-        <v>500</v>
-      </c>
-      <c r="F8" s="14" t="n">
+      <c r="D8" s="13" t="n">
+        <v>1030</v>
+      </c>
+      <c r="E8" s="13" t="n">
+        <v>258</v>
+      </c>
+      <c r="F8" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="G8" s="14" t="n">
+      <c r="G8" s="13" t="n">
         <v>0.15</v>
       </c>
-      <c r="H8" s="15">
+      <c r="H8" s="14">
         <f>B8*D8+E8*((B8-1)*B8/2)</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="14" t="n">
+      <c r="A9" s="13" t="n">
         <v>6</v>
       </c>
-      <c r="B9" s="14" t="n">
+      <c r="B9" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="C9" s="14" t="n">
+      <c r="C9" s="13" t="n">
         <v>7</v>
       </c>
-      <c r="D9" s="14" t="n">
-        <v>6000</v>
-      </c>
-      <c r="E9" s="14" t="n">
-        <v>800</v>
-      </c>
-      <c r="F9" s="14" t="n">
+      <c r="D9" s="13" t="n">
+        <v>6240</v>
+      </c>
+      <c r="E9" s="13" t="n">
+        <v>1560</v>
+      </c>
+      <c r="F9" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="G9" s="14" t="n">
-        <v>150</v>
-      </c>
-      <c r="H9" s="15">
+      <c r="G9" s="13" t="n">
+        <v>312</v>
+      </c>
+      <c r="H9" s="14">
         <f>B9*D9+E9*((B9-1)*B9/2)</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="14" t="n">
+      <c r="A10" s="13" t="n">
         <v>7</v>
       </c>
-      <c r="B10" s="14" t="n">
+      <c r="B10" s="13" t="n">
         <v>9</v>
       </c>
-      <c r="C10" s="14" t="n">
+      <c r="C10" s="13" t="n">
         <v>8</v>
       </c>
-      <c r="D10" s="14" t="n">
-        <v>10000</v>
-      </c>
-      <c r="E10" s="14" t="n">
-        <v>1500</v>
-      </c>
-      <c r="F10" s="14" t="n">
+      <c r="D10" s="13" t="n">
+        <v>6617</v>
+      </c>
+      <c r="E10" s="13" t="n">
+        <v>1654</v>
+      </c>
+      <c r="F10" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="G10" s="14" t="n">
-        <v>250</v>
-      </c>
-      <c r="H10" s="15">
+      <c r="G10" s="13" t="n">
+        <v>530</v>
+      </c>
+      <c r="H10" s="14">
         <f>B10*D10+E10*((B10-1)*B10/2)</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="14" t="n">
+      <c r="A11" s="13" t="n">
         <v>8</v>
       </c>
-      <c r="B11" s="14" t="n">
+      <c r="B11" s="13" t="n">
         <v>9</v>
       </c>
-      <c r="C11" s="14" t="n">
+      <c r="C11" s="13" t="n">
         <v>9</v>
       </c>
-      <c r="D11" s="14" t="n">
-        <v>17000</v>
-      </c>
-      <c r="E11" s="14" t="n">
-        <v>2500</v>
-      </c>
-      <c r="F11" s="14" t="n">
+      <c r="D11" s="13" t="n">
+        <v>13442</v>
+      </c>
+      <c r="E11" s="13" t="n">
+        <v>3360</v>
+      </c>
+      <c r="F11" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="G11" s="14" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="H11" s="15">
+      <c r="G11" s="13" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="H11" s="14">
         <f>B11*D11+E11*((B11-1)*B11/2)</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="14" t="n">
+      <c r="A12" s="13" t="n">
         <v>9</v>
       </c>
-      <c r="B12" s="14" t="n">
+      <c r="B12" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="C12" s="14" t="n">
+      <c r="C12" s="13" t="n">
         <v>10</v>
       </c>
-      <c r="D12" s="14" t="n">
-        <v>28000</v>
-      </c>
-      <c r="E12" s="14" t="n">
-        <v>4000</v>
-      </c>
-      <c r="F12" s="14" t="n">
+      <c r="D12" s="13" t="n">
+        <v>81955</v>
+      </c>
+      <c r="E12" s="13" t="n">
+        <v>20489</v>
+      </c>
+      <c r="F12" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="G12" s="14" t="n">
+      <c r="G12" s="13" t="n">
         <v>0.2</v>
       </c>
-      <c r="H12" s="15">
+      <c r="H12" s="14">
         <f>B12*D12+E12*((B12-1)*B12/2)</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="14" t="n">
+      <c r="A13" s="13" t="n">
         <v>10</v>
       </c>
-      <c r="B13" s="14" t="n">
+      <c r="B13" s="13" t="n">
         <v>12</v>
       </c>
-      <c r="C13" s="14" t="n">
+      <c r="C13" s="13" t="n">
         <v>11</v>
       </c>
-      <c r="D13" s="14" t="n">
-        <v>45000</v>
-      </c>
-      <c r="E13" s="14" t="n">
-        <v>6000</v>
-      </c>
-      <c r="F13" s="14" t="n">
+      <c r="D13" s="13" t="n">
+        <v>26658</v>
+      </c>
+      <c r="E13" s="13" t="n">
+        <v>6664</v>
+      </c>
+      <c r="F13" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="G13" s="14" t="n">
-        <v>600</v>
-      </c>
-      <c r="H13" s="15">
+      <c r="G13" s="13" t="n">
+        <v>5065</v>
+      </c>
+      <c r="H13" s="14">
         <f>B13*D13+E13*((B13-1)*B13/2)</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="14" t="n">
+      <c r="A14" s="13" t="n">
         <v>11</v>
       </c>
-      <c r="B14" s="14" t="n">
+      <c r="B14" s="13" t="n">
         <v>7</v>
       </c>
-      <c r="C14" s="14" t="n">
+      <c r="C14" s="13" t="n">
         <v>12</v>
       </c>
-      <c r="D14" s="14" t="n">
-        <v>75000</v>
-      </c>
-      <c r="E14" s="14" t="n">
-        <v>10000</v>
-      </c>
-      <c r="F14" s="14" t="n">
+      <c r="D14" s="13" t="n">
+        <v>84992</v>
+      </c>
+      <c r="E14" s="13" t="n">
+        <v>21248</v>
+      </c>
+      <c r="F14" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="G14" s="14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="H14" s="15">
+      <c r="G14" s="13" t="n">
+        <v>4627</v>
+      </c>
+      <c r="H14" s="14">
         <f>B14*D14+E14*((B14-1)*B14/2)</f>
         <v/>
       </c>
@@ -2050,102 +2728,101 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:C6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="42" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" style="16" min="1" max="2"/>
+    <col width="42" customWidth="1" style="16" min="3" max="3"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="12" t="inlineStr">
+    <row r="1" ht="30" customHeight="1" s="16">
+      <c r="A1" s="11" t="inlineStr">
         <is>
           <t>#설정 키</t>
         </is>
       </c>
-      <c r="B1" s="12" t="inlineStr">
+      <c r="B1" s="11" t="inlineStr">
         <is>
           <t>값</t>
         </is>
       </c>
-      <c r="C1" s="12" t="inlineStr">
+      <c r="C1" s="11" t="inlineStr">
         <is>
           <t>설명</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="13" t="inlineStr">
+    <row r="2" ht="17.25" customHeight="1" s="16">
+      <c r="A2" s="12" t="inlineStr">
         <is>
           <t>key</t>
         </is>
       </c>
-      <c r="B2" s="13" t="inlineStr">
+      <c r="B2" s="12" t="inlineStr">
         <is>
           <t>value</t>
         </is>
       </c>
-      <c r="C2" s="13" t="inlineStr">
+      <c r="C2" s="12" t="inlineStr">
         <is>
           <t>note</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="14" t="inlineStr">
+      <c r="A3" s="13" t="inlineStr">
         <is>
           <t>moonDamage</t>
         </is>
       </c>
-      <c r="B3" s="14" t="n">
+      <c r="B3" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="C3" s="14" t="inlineStr">
+      <c r="C3" s="13" t="inlineStr">
         <is>
           <t>달 자동공격 1회 데미지</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="14" t="inlineStr">
+      <c r="A4" s="13" t="inlineStr">
         <is>
           <t>moonInterval</t>
         </is>
       </c>
-      <c r="B4" s="14" t="n">
+      <c r="B4" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="C4" s="14" t="inlineStr">
+      <c r="C4" s="13" t="inlineStr">
         <is>
           <t>달 자동공격 주기(초)</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="14" t="inlineStr">
+      <c r="A5" s="13" t="inlineStr">
         <is>
           <t>bossDuration</t>
         </is>
       </c>
-      <c r="B5" s="14" t="n">
+      <c r="B5" s="13" t="n">
         <v>20</v>
       </c>
-      <c r="C5" s="14" t="inlineStr">
+      <c r="C5" s="13" t="inlineStr">
         <is>
           <t>보스전 제한시간(초)</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="14" t="inlineStr">
+      <c r="A6" s="13" t="inlineStr">
         <is>
           <t>killsRequired</t>
         </is>
       </c>
-      <c r="B6" s="14" t="n">
+      <c r="B6" s="13" t="n">
         <v>50</v>
       </c>
-      <c r="C6" s="14" t="inlineStr">
+      <c r="C6" s="13" t="inlineStr">
         <is>
           <t>보스 도전에 필요한 일반 몬스터 처치 수</t>
         </is>

--- a/DataTable/내일할래_데이터테이블.xlsx
+++ b/DataTable/내일할래_데이터테이블.xlsx
@@ -1161,7 +1161,7 @@
         <v>3</v>
       </c>
       <c r="B6" s="13" t="n">
-        <v>12921</v>
+        <v>11433</v>
       </c>
       <c r="C6" s="13" t="n">
         <v>350</v>
@@ -1172,10 +1172,10 @@
         <v>4</v>
       </c>
       <c r="B7" s="13" t="n">
-        <v>32037</v>
+        <v>23203</v>
       </c>
       <c r="C7" s="13" t="n">
-        <v>800</v>
+        <v>700</v>
       </c>
     </row>
     <row r="8">
@@ -1183,10 +1183,10 @@
         <v>5</v>
       </c>
       <c r="B8" s="13" t="n">
-        <v>88506</v>
+        <v>61077</v>
       </c>
       <c r="C8" s="13" t="n">
-        <v>1700</v>
+        <v>1250</v>
       </c>
     </row>
     <row r="9">
@@ -1194,10 +1194,10 @@
         <v>6</v>
       </c>
       <c r="B9" s="13" t="n">
-        <v>257034</v>
+        <v>183355</v>
       </c>
       <c r="C9" s="13" t="n">
-        <v>4650</v>
+        <v>3150</v>
       </c>
     </row>
     <row r="10">
@@ -1205,10 +1205,10 @@
         <v>7</v>
       </c>
       <c r="B10" s="13" t="n">
-        <v>852309</v>
+        <v>666561</v>
       </c>
       <c r="C10" s="13" t="n">
-        <v>14050</v>
+        <v>8250</v>
       </c>
     </row>
     <row r="11">
@@ -1216,10 +1216,10 @@
         <v>8</v>
       </c>
       <c r="B11" s="13" t="n">
-        <v>1855963</v>
+        <v>1342246</v>
       </c>
       <c r="C11" s="13" t="n">
-        <v>35750</v>
+        <v>22100</v>
       </c>
     </row>
     <row r="12">
@@ -1227,10 +1227,10 @@
         <v>9</v>
       </c>
       <c r="B12" s="13" t="n">
-        <v>3735088</v>
+        <v>3131890</v>
       </c>
       <c r="C12" s="13" t="n">
-        <v>72600</v>
+        <v>47600</v>
       </c>
     </row>
     <row r="13">
@@ -1238,10 +1238,10 @@
         <v>10</v>
       </c>
       <c r="B13" s="13" t="n">
-        <v>4465671</v>
+        <v>3881646</v>
       </c>
       <c r="C13" s="13" t="n">
-        <v>135250</v>
+        <v>89000</v>
       </c>
     </row>
     <row r="14">
@@ -1249,10 +1249,10 @@
         <v>11</v>
       </c>
       <c r="B14" s="13" t="n">
-        <v>4210851</v>
+        <v>5147446</v>
       </c>
       <c r="C14" s="13" t="n">
-        <v>227900</v>
+        <v>178700</v>
       </c>
     </row>
     <row r="15">
@@ -1260,10 +1260,10 @@
         <v>12</v>
       </c>
       <c r="B15" s="13" t="n">
-        <v>5743061</v>
+        <v>4446739</v>
       </c>
       <c r="C15" s="13" t="n">
-        <v>312350</v>
+        <v>250450</v>
       </c>
     </row>
   </sheetData>
@@ -1277,7 +1277,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D28"/>
+  <dimension ref="A1:D41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
     <col width="20" customWidth="1" style="16" min="1" max="4"/>
@@ -1335,7 +1335,7 @@
         <v>0</v>
       </c>
       <c r="C3" s="13" t="n">
-        <v>148</v>
+        <v>140</v>
       </c>
       <c r="D3" s="13" t="n">
         <v>1</v>
@@ -1349,7 +1349,7 @@
         <v>1</v>
       </c>
       <c r="C4" s="13" t="n">
-        <v>182</v>
+        <v>165</v>
       </c>
       <c r="D4" s="13" t="n">
         <v>1</v>
@@ -1357,16 +1357,16 @@
     </row>
     <row r="5">
       <c r="A5" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="B5" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="C5" s="13" t="n">
+        <v>190</v>
+      </c>
+      <c r="D5" s="13" t="n">
         <v>1</v>
-      </c>
-      <c r="B5" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="C5" s="13" t="n">
-        <v>270</v>
-      </c>
-      <c r="D5" s="13" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -1374,321 +1374,503 @@
         <v>1</v>
       </c>
       <c r="B6" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C6" s="13" t="n">
-        <v>330</v>
+        <v>255</v>
       </c>
       <c r="D6" s="13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="B7" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" s="13" t="n">
+        <v>300</v>
+      </c>
+      <c r="D7" s="13" t="n">
         <v>2</v>
-      </c>
-      <c r="B7" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="C7" s="13" t="n">
-        <v>513</v>
-      </c>
-      <c r="D7" s="13" t="n">
-        <v>4</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="B8" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="B8" s="13" t="n">
-        <v>1</v>
-      </c>
       <c r="C8" s="13" t="n">
-        <v>627</v>
+        <v>345</v>
       </c>
       <c r="D8" s="13" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B9" s="13" t="n">
         <v>0</v>
       </c>
       <c r="C9" s="13" t="n">
-        <v>918</v>
+        <v>484</v>
       </c>
       <c r="D9" s="13" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B10" s="13" t="n">
         <v>1</v>
       </c>
       <c r="C10" s="13" t="n">
-        <v>1122</v>
+        <v>570</v>
       </c>
       <c r="D10" s="13" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="13" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B11" s="13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C11" s="13" t="n">
-        <v>1958</v>
+        <v>656</v>
       </c>
       <c r="D11" s="13" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="13" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B12" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C12" s="13" t="n">
-        <v>2392</v>
+        <v>867</v>
       </c>
       <c r="D12" s="13" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="13" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B13" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C13" s="13" t="n">
-        <v>4280</v>
+        <v>1020</v>
       </c>
       <c r="D13" s="13" t="n">
-        <v>34</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="13" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B14" s="13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C14" s="13" t="n">
-        <v>5230</v>
+        <v>1173</v>
       </c>
       <c r="D14" s="13" t="n">
-        <v>42</v>
+        <v>8</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="13" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B15" s="13" t="n">
         <v>0</v>
       </c>
       <c r="C15" s="13" t="n">
-        <v>11624</v>
+        <v>1721</v>
       </c>
       <c r="D15" s="13" t="n">
-        <v>93</v>
+        <v>12</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="13" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B16" s="13" t="n">
         <v>1</v>
       </c>
       <c r="C16" s="13" t="n">
-        <v>14207</v>
+        <v>2025</v>
       </c>
       <c r="D16" s="13" t="n">
-        <v>114</v>
+        <v>14</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="13" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B17" s="13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C17" s="13" t="n">
-        <v>35154</v>
+        <v>2329</v>
       </c>
       <c r="D17" s="13" t="n">
-        <v>281</v>
+        <v>16</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="13" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B18" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C18" s="13" t="n">
-        <v>42966</v>
+        <v>3022</v>
       </c>
       <c r="D18" s="13" t="n">
-        <v>344</v>
+        <v>21</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="13" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B19" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C19" s="13" t="n">
-        <v>89356</v>
+        <v>3555</v>
       </c>
       <c r="D19" s="13" t="n">
-        <v>715</v>
+        <v>25</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="13" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B20" s="13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C20" s="13" t="n">
-        <v>109214</v>
+        <v>4088</v>
       </c>
       <c r="D20" s="13" t="n">
-        <v>874</v>
+        <v>29</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="13" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B21" s="13" t="n">
         <v>0</v>
       </c>
       <c r="C21" s="13" t="n">
-        <v>181453</v>
+        <v>7688</v>
       </c>
       <c r="D21" s="13" t="n">
-        <v>1452</v>
+        <v>54</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="13" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B22" s="13" t="n">
         <v>1</v>
       </c>
       <c r="C22" s="13" t="n">
-        <v>221775</v>
+        <v>9045</v>
       </c>
       <c r="D22" s="13" t="n">
-        <v>1774</v>
+        <v>63</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="13" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="B23" s="13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C23" s="13" t="n">
-        <v>338099</v>
+        <v>10402</v>
       </c>
       <c r="D23" s="13" t="n">
-        <v>2705</v>
+        <v>73</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="13" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B24" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C24" s="13" t="n">
-        <v>413233</v>
+        <v>20094</v>
       </c>
       <c r="D24" s="13" t="n">
-        <v>3306</v>
+        <v>141</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="13" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B25" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C25" s="13" t="n">
-        <v>569765</v>
+        <v>23640</v>
       </c>
       <c r="D25" s="13" t="n">
-        <v>4558</v>
+        <v>165</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="13" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B26" s="13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C26" s="13" t="n">
-        <v>696379</v>
+        <v>27186</v>
       </c>
       <c r="D26" s="13" t="n">
-        <v>5571</v>
+        <v>190</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="13" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B27" s="13" t="n">
         <v>0</v>
       </c>
       <c r="C27" s="13" t="n">
-        <v>780860</v>
+        <v>53716</v>
       </c>
       <c r="D27" s="13" t="n">
-        <v>6247</v>
+        <v>376</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="13" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B28" s="13" t="n">
         <v>1</v>
       </c>
       <c r="C28" s="13" t="n">
-        <v>954384</v>
+        <v>63195</v>
       </c>
       <c r="D28" s="13" t="n">
-        <v>7635</v>
+        <v>442</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="13" t="n">
+        <v>8</v>
+      </c>
+      <c r="B29" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="C29" s="13" t="n">
+        <v>72674</v>
+      </c>
+      <c r="D29" s="13" t="n">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="13" t="n">
+        <v>9</v>
+      </c>
+      <c r="B30" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="C30" s="13" t="n">
+        <v>115606</v>
+      </c>
+      <c r="D30" s="13" t="n">
+        <v>809</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="13" t="n">
+        <v>9</v>
+      </c>
+      <c r="B31" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="C31" s="13" t="n">
+        <v>136007</v>
+      </c>
+      <c r="D31" s="13" t="n">
+        <v>952</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="13" t="n">
+        <v>9</v>
+      </c>
+      <c r="B32" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="C32" s="13" t="n">
+        <v>156408</v>
+      </c>
+      <c r="D32" s="13" t="n">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="13" t="n">
+        <v>10</v>
+      </c>
+      <c r="B33" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="C33" s="13" t="n">
+        <v>216121</v>
+      </c>
+      <c r="D33" s="13" t="n">
+        <v>1513</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="13" t="n">
+        <v>10</v>
+      </c>
+      <c r="B34" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="C34" s="13" t="n">
+        <v>254260</v>
+      </c>
+      <c r="D34" s="13" t="n">
+        <v>1780</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="13" t="n">
+        <v>10</v>
+      </c>
+      <c r="B35" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="C35" s="13" t="n">
+        <v>292399</v>
+      </c>
+      <c r="D35" s="13" t="n">
+        <v>2047</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="13" t="n">
+        <v>11</v>
+      </c>
+      <c r="B36" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="C36" s="13" t="n">
+        <v>433927</v>
+      </c>
+      <c r="D36" s="13" t="n">
+        <v>3037</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="13" t="n">
+        <v>11</v>
+      </c>
+      <c r="B37" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="C37" s="13" t="n">
+        <v>510502</v>
+      </c>
+      <c r="D37" s="13" t="n">
+        <v>3574</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="13" t="n">
+        <v>11</v>
+      </c>
+      <c r="B38" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="C38" s="13" t="n">
+        <v>587077</v>
+      </c>
+      <c r="D38" s="13" t="n">
+        <v>4110</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B39" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="C39" s="13" t="n">
+        <v>608195</v>
+      </c>
+      <c r="D39" s="13" t="n">
+        <v>4257</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B40" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="C40" s="13" t="n">
+        <v>715524</v>
+      </c>
+      <c r="D40" s="13" t="n">
+        <v>5009</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B41" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="C41" s="13" t="n">
+        <v>822853</v>
+      </c>
+      <c r="D41" s="13" t="n">
+        <v>5760</v>
       </c>
     </row>
   </sheetData>
@@ -2457,10 +2639,10 @@
         <v>3</v>
       </c>
       <c r="D5" s="13" t="n">
-        <v>123</v>
+        <v>108</v>
       </c>
       <c r="E5" s="13" t="n">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="F5" s="13" t="n">
         <v>1</v>
@@ -2484,16 +2666,16 @@
         <v>4</v>
       </c>
       <c r="D6" s="13" t="n">
-        <v>464</v>
+        <v>382</v>
       </c>
       <c r="E6" s="13" t="n">
-        <v>116</v>
+        <v>95</v>
       </c>
       <c r="F6" s="13" t="n">
         <v>0</v>
       </c>
       <c r="G6" s="13" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H6" s="14">
         <f>B6*D6+E6*((B6-1)*B6/2)</f>
@@ -2511,10 +2693,10 @@
         <v>5</v>
       </c>
       <c r="D7" s="13" t="n">
-        <v>317</v>
+        <v>208</v>
       </c>
       <c r="E7" s="13" t="n">
-        <v>79</v>
+        <v>52</v>
       </c>
       <c r="F7" s="13" t="n">
         <v>2</v>
@@ -2538,10 +2720,10 @@
         <v>6</v>
       </c>
       <c r="D8" s="13" t="n">
-        <v>1030</v>
+        <v>630</v>
       </c>
       <c r="E8" s="13" t="n">
-        <v>258</v>
+        <v>158</v>
       </c>
       <c r="F8" s="13" t="n">
         <v>3</v>
@@ -2565,16 +2747,16 @@
         <v>7</v>
       </c>
       <c r="D9" s="13" t="n">
-        <v>6240</v>
+        <v>3300</v>
       </c>
       <c r="E9" s="13" t="n">
-        <v>1560</v>
+        <v>825</v>
       </c>
       <c r="F9" s="13" t="n">
         <v>1</v>
       </c>
       <c r="G9" s="13" t="n">
-        <v>312</v>
+        <v>189</v>
       </c>
       <c r="H9" s="14">
         <f>B9*D9+E9*((B9-1)*B9/2)</f>
@@ -2592,16 +2774,16 @@
         <v>8</v>
       </c>
       <c r="D10" s="13" t="n">
-        <v>6617</v>
+        <v>3683</v>
       </c>
       <c r="E10" s="13" t="n">
-        <v>1654</v>
+        <v>921</v>
       </c>
       <c r="F10" s="13" t="n">
         <v>0</v>
       </c>
       <c r="G10" s="13" t="n">
-        <v>530</v>
+        <v>337</v>
       </c>
       <c r="H10" s="14">
         <f>B10*D10+E10*((B10-1)*B10/2)</f>
@@ -2619,10 +2801,10 @@
         <v>9</v>
       </c>
       <c r="D11" s="13" t="n">
-        <v>13442</v>
+        <v>7933</v>
       </c>
       <c r="E11" s="13" t="n">
-        <v>3360</v>
+        <v>1983</v>
       </c>
       <c r="F11" s="13" t="n">
         <v>2</v>
@@ -2646,10 +2828,10 @@
         <v>10</v>
       </c>
       <c r="D12" s="13" t="n">
-        <v>81955</v>
+        <v>48545</v>
       </c>
       <c r="E12" s="13" t="n">
-        <v>20489</v>
+        <v>12136</v>
       </c>
       <c r="F12" s="13" t="n">
         <v>3</v>
@@ -2673,16 +2855,16 @@
         <v>11</v>
       </c>
       <c r="D13" s="13" t="n">
-        <v>26658</v>
+        <v>18811</v>
       </c>
       <c r="E13" s="13" t="n">
-        <v>6664</v>
+        <v>4703</v>
       </c>
       <c r="F13" s="13" t="n">
         <v>1</v>
       </c>
       <c r="G13" s="13" t="n">
-        <v>5065</v>
+        <v>4084</v>
       </c>
       <c r="H13" s="14">
         <f>B13*D13+E13*((B13-1)*B13/2)</f>
@@ -2700,16 +2882,16 @@
         <v>12</v>
       </c>
       <c r="D14" s="13" t="n">
-        <v>84992</v>
+        <v>61335</v>
       </c>
       <c r="E14" s="13" t="n">
-        <v>21248</v>
+        <v>15334</v>
       </c>
       <c r="F14" s="13" t="n">
         <v>0</v>
       </c>
       <c r="G14" s="13" t="n">
-        <v>4627</v>
+        <v>3816</v>
       </c>
       <c r="H14" s="14">
         <f>B14*D14+E14*((B14-1)*B14/2)</f>

--- a/DataTable/내일할래_데이터테이블.xlsx
+++ b/DataTable/내일할래_데이터테이블.xlsx
@@ -2582,7 +2582,7 @@
         <v>5</v>
       </c>
       <c r="C3" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D3" s="13" t="n">
         <v>50</v>
@@ -2609,7 +2609,7 @@
         <v>10</v>
       </c>
       <c r="C4" s="13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D4" s="13" t="n">
         <v>50</v>
@@ -2636,7 +2636,7 @@
         <v>6</v>
       </c>
       <c r="C5" s="13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D5" s="13" t="n">
         <v>108</v>
@@ -2663,7 +2663,7 @@
         <v>4</v>
       </c>
       <c r="C6" s="13" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D6" s="13" t="n">
         <v>382</v>
@@ -2690,7 +2690,7 @@
         <v>9</v>
       </c>
       <c r="C7" s="13" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D7" s="13" t="n">
         <v>208</v>
@@ -2717,7 +2717,7 @@
         <v>8</v>
       </c>
       <c r="C8" s="13" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D8" s="13" t="n">
         <v>630</v>
@@ -2744,7 +2744,7 @@
         <v>5</v>
       </c>
       <c r="C9" s="13" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D9" s="13" t="n">
         <v>3300</v>
@@ -2771,7 +2771,7 @@
         <v>9</v>
       </c>
       <c r="C10" s="13" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D10" s="13" t="n">
         <v>3683</v>
@@ -2798,7 +2798,7 @@
         <v>9</v>
       </c>
       <c r="C11" s="13" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D11" s="13" t="n">
         <v>7933</v>
@@ -2825,7 +2825,7 @@
         <v>4</v>
       </c>
       <c r="C12" s="13" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D12" s="13" t="n">
         <v>48545</v>
@@ -2852,7 +2852,7 @@
         <v>12</v>
       </c>
       <c r="C13" s="13" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D13" s="13" t="n">
         <v>18811</v>
@@ -2879,7 +2879,7 @@
         <v>7</v>
       </c>
       <c r="C14" s="13" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D14" s="13" t="n">
         <v>61335</v>

--- a/DataTable/내일할래_데이터테이블.xlsx
+++ b/DataTable/내일할래_데이터테이블.xlsx
@@ -1338,7 +1338,7 @@
         <v>140</v>
       </c>
       <c r="D3" s="13" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4">
@@ -1352,7 +1352,7 @@
         <v>165</v>
       </c>
       <c r="D4" s="13" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5">
@@ -1366,7 +1366,7 @@
         <v>190</v>
       </c>
       <c r="D5" s="13" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6">
@@ -1380,7 +1380,7 @@
         <v>255</v>
       </c>
       <c r="D6" s="13" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7">
@@ -1394,7 +1394,7 @@
         <v>300</v>
       </c>
       <c r="D7" s="13" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8">
@@ -1408,7 +1408,7 @@
         <v>345</v>
       </c>
       <c r="D8" s="13" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9">
@@ -1422,7 +1422,7 @@
         <v>484</v>
       </c>
       <c r="D9" s="13" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10">
@@ -1436,7 +1436,7 @@
         <v>570</v>
       </c>
       <c r="D10" s="13" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11">
@@ -1450,7 +1450,7 @@
         <v>656</v>
       </c>
       <c r="D11" s="13" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12">
@@ -1464,7 +1464,7 @@
         <v>867</v>
       </c>
       <c r="D12" s="13" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="13">
@@ -1478,7 +1478,7 @@
         <v>1020</v>
       </c>
       <c r="D13" s="13" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="14">
@@ -1492,7 +1492,7 @@
         <v>1173</v>
       </c>
       <c r="D14" s="13" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="15">

--- a/DataTable/내일할래_데이터테이블.xlsx
+++ b/DataTable/내일할래_데이터테이블.xlsx
@@ -2909,7 +2909,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
     <col width="20" customWidth="1" style="16" min="1" max="2"/>
@@ -3010,6 +3010,36 @@
         </is>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" s="13" t="inlineStr">
+        <is>
+          <t>offlineRate</t>
+        </is>
+      </c>
+      <c r="B7" s="13" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="C7" s="13" t="inlineStr">
+        <is>
+          <t>오프라인 초당 지급 배율 (현재 스테이지 몬스터 평균 보상 x 이 값 x 초)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="13" t="inlineStr">
+        <is>
+          <t>offlineMaxHours</t>
+        </is>
+      </c>
+      <c r="B8" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="C8" s="13" t="inlineStr">
+        <is>
+          <t>오프라인 보상 최대 인정 시간(시간). 더 꺼둬도 이 이상은 안 쌓임</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/DataTable/내일할래_데이터테이블.xlsx
+++ b/DataTable/내일할래_데이터테이블.xlsx
@@ -2243,7 +2243,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:H10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
     <col width="20" customWidth="1" style="16" min="1" max="6"/>
@@ -2280,6 +2280,16 @@
           <t>달 주기 감소(초)</t>
         </is>
       </c>
+      <c r="G1" s="11" t="inlineStr">
+        <is>
+          <t>달 치명타 확률 증가</t>
+        </is>
+      </c>
+      <c r="H1" s="11" t="inlineStr">
+        <is>
+          <t>달 치명타 피해 증가</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="17.25" customHeight="1" s="16">
       <c r="A2" s="12" t="inlineStr">
@@ -2310,6 +2320,16 @@
       <c r="F2" s="12" t="inlineStr">
         <is>
           <t>moonIntervalReduction</t>
+        </is>
+      </c>
+      <c r="G2" s="12" t="inlineStr">
+        <is>
+          <t>moonCritChanceBonus</t>
+        </is>
+      </c>
+      <c r="H2" s="12" t="inlineStr">
+        <is>
+          <t>moonCritDamageBonus</t>
         </is>
       </c>
     </row>
@@ -2332,6 +2352,12 @@
       <c r="F3" s="13" t="n">
         <v>0.06</v>
       </c>
+      <c r="G3" s="13" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="H3" s="13" t="n">
+        <v>0.04</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="13" t="n">
@@ -2352,6 +2378,12 @@
       <c r="F4" s="13" t="n">
         <v>0.06</v>
       </c>
+      <c r="G4" s="13" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="H4" s="13" t="n">
+        <v>0.06</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="13" t="n">
@@ -2372,6 +2404,12 @@
       <c r="F5" s="13" t="n">
         <v>0.06</v>
       </c>
+      <c r="G5" s="13" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="H5" s="13" t="n">
+        <v>0.08</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="13" t="n">
@@ -2392,6 +2430,12 @@
       <c r="F6" s="13" t="n">
         <v>0.06</v>
       </c>
+      <c r="G6" s="13" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="H6" s="13" t="n">
+        <v>0.1</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="13" t="n">
@@ -2412,6 +2456,12 @@
       <c r="F7" s="13" t="n">
         <v>0.06</v>
       </c>
+      <c r="G7" s="13" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="H7" s="13" t="n">
+        <v>0.12</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="13" t="n">
@@ -2432,6 +2482,12 @@
       <c r="F8" s="13" t="n">
         <v>0.06</v>
       </c>
+      <c r="G8" s="13" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="H8" s="13" t="n">
+        <v>0.14</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="13" t="n">
@@ -2452,6 +2508,12 @@
       <c r="F9" s="13" t="n">
         <v>0.06</v>
       </c>
+      <c r="G9" s="13" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="H9" s="13" t="n">
+        <v>0.16</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="13" t="n">
@@ -2471,6 +2533,12 @@
       </c>
       <c r="F10" s="13" t="n">
         <v>0.06</v>
+      </c>
+      <c r="G10" s="13" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="H10" s="13" t="n">
+        <v>0.18</v>
       </c>
     </row>
   </sheetData>
@@ -2518,7 +2586,7 @@
       </c>
       <c r="F1" s="11" t="inlineStr">
         <is>
-          <t>효과 종류(0클릭/1달뎀/2달속도/3코인)</t>
+          <t>효과 종류(0클릭/1달뎀/2달속도/3코인/4치명확률/5치명피해)</t>
         </is>
       </c>
       <c r="G1" s="11" t="inlineStr">
@@ -2672,10 +2740,10 @@
         <v>95</v>
       </c>
       <c r="F6" s="13" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G6" s="13" t="n">
-        <v>11</v>
+        <v>0.03</v>
       </c>
       <c r="H6" s="14">
         <f>B6*D6+E6*((B6-1)*B6/2)</f>
@@ -2780,10 +2848,10 @@
         <v>921</v>
       </c>
       <c r="F10" s="13" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G10" s="13" t="n">
-        <v>337</v>
+        <v>0.3</v>
       </c>
       <c r="H10" s="14">
         <f>B10*D10+E10*((B10-1)*B10/2)</f>
@@ -2861,10 +2929,10 @@
         <v>4703</v>
       </c>
       <c r="F13" s="13" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G13" s="13" t="n">
-        <v>4084</v>
+        <v>0.05</v>
       </c>
       <c r="H13" s="14">
         <f>B13*D13+E13*((B13-1)*B13/2)</f>
@@ -2909,7 +2977,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:C10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
     <col width="20" customWidth="1" style="16" min="1" max="2"/>
@@ -3040,6 +3108,36 @@
         </is>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" s="13" t="inlineStr">
+        <is>
+          <t>critChance</t>
+        </is>
+      </c>
+      <c r="B9" s="13" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="C9" s="13" t="inlineStr">
+        <is>
+          <t>기본 치명타 확률 (0.05 = 5%). 클릭·달 공통</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="13" t="inlineStr">
+        <is>
+          <t>critMultiplier</t>
+        </is>
+      </c>
+      <c r="B10" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="C10" s="13" t="inlineStr">
+        <is>
+          <t>기본 치명타 피해 배율 (2 = 200%). 클릭·달 공통</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/DataTable/내일할래_데이터테이블.xlsx
+++ b/DataTable/내일할래_데이터테이블.xlsx
@@ -1128,10 +1128,10 @@
         <v>0</v>
       </c>
       <c r="B3" s="13" t="n">
-        <v>1788</v>
+        <v>3335</v>
       </c>
       <c r="C3" s="13" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
     </row>
     <row r="4">
@@ -1139,10 +1139,10 @@
         <v>1</v>
       </c>
       <c r="B4" s="13" t="n">
-        <v>3895</v>
+        <v>3602</v>
       </c>
       <c r="C4" s="13" t="n">
-        <v>100</v>
+        <v>300</v>
       </c>
     </row>
     <row r="5">
@@ -1150,10 +1150,10 @@
         <v>2</v>
       </c>
       <c r="B5" s="13" t="n">
-        <v>6868</v>
+        <v>25228</v>
       </c>
       <c r="C5" s="13" t="n">
-        <v>200</v>
+        <v>350</v>
       </c>
     </row>
     <row r="6">
@@ -1161,10 +1161,10 @@
         <v>3</v>
       </c>
       <c r="B6" s="13" t="n">
-        <v>11433</v>
+        <v>73320</v>
       </c>
       <c r="C6" s="13" t="n">
-        <v>350</v>
+        <v>1550</v>
       </c>
     </row>
     <row r="7">
@@ -1172,10 +1172,10 @@
         <v>4</v>
       </c>
       <c r="B7" s="13" t="n">
-        <v>23203</v>
+        <v>250629</v>
       </c>
       <c r="C7" s="13" t="n">
-        <v>700</v>
+        <v>4750</v>
       </c>
     </row>
     <row r="8">
@@ -1183,10 +1183,10 @@
         <v>5</v>
       </c>
       <c r="B8" s="13" t="n">
-        <v>61077</v>
+        <v>821776</v>
       </c>
       <c r="C8" s="13" t="n">
-        <v>1250</v>
+        <v>17400</v>
       </c>
     </row>
     <row r="9">
@@ -1194,10 +1194,10 @@
         <v>6</v>
       </c>
       <c r="B9" s="13" t="n">
-        <v>183355</v>
+        <v>590049</v>
       </c>
       <c r="C9" s="13" t="n">
-        <v>3150</v>
+        <v>61700</v>
       </c>
     </row>
     <row r="10">
@@ -1205,10 +1205,10 @@
         <v>7</v>
       </c>
       <c r="B10" s="13" t="n">
-        <v>666561</v>
+        <v>1758449</v>
       </c>
       <c r="C10" s="13" t="n">
-        <v>8250</v>
+        <v>114250</v>
       </c>
     </row>
     <row r="11">
@@ -1216,10 +1216,10 @@
         <v>8</v>
       </c>
       <c r="B11" s="13" t="n">
-        <v>1342246</v>
+        <v>210988</v>
       </c>
       <c r="C11" s="13" t="n">
-        <v>22100</v>
+        <v>335650</v>
       </c>
     </row>
     <row r="12">
@@ -1227,10 +1227,10 @@
         <v>9</v>
       </c>
       <c r="B12" s="13" t="n">
-        <v>3131890</v>
+        <v>2802589</v>
       </c>
       <c r="C12" s="13" t="n">
-        <v>47600</v>
+        <v>461100</v>
       </c>
     </row>
     <row r="13">
@@ -1238,10 +1238,10 @@
         <v>10</v>
       </c>
       <c r="B13" s="13" t="n">
-        <v>3881646</v>
+        <v>4668293</v>
       </c>
       <c r="C13" s="13" t="n">
-        <v>89000</v>
+        <v>635750</v>
       </c>
     </row>
     <row r="14">
@@ -1249,10 +1249,10 @@
         <v>11</v>
       </c>
       <c r="B14" s="13" t="n">
-        <v>5147446</v>
+        <v>6598746</v>
       </c>
       <c r="C14" s="13" t="n">
-        <v>178700</v>
+        <v>755850</v>
       </c>
     </row>
     <row r="15">
@@ -1260,10 +1260,10 @@
         <v>12</v>
       </c>
       <c r="B15" s="13" t="n">
-        <v>4446739</v>
+        <v>11019739</v>
       </c>
       <c r="C15" s="13" t="n">
-        <v>250450</v>
+        <v>865800</v>
       </c>
     </row>
   </sheetData>
@@ -1338,7 +1338,7 @@
         <v>140</v>
       </c>
       <c r="D3" s="13" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -1352,7 +1352,7 @@
         <v>165</v>
       </c>
       <c r="D4" s="13" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -1366,7 +1366,7 @@
         <v>190</v>
       </c>
       <c r="D5" s="13" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -1377,7 +1377,7 @@
         <v>0</v>
       </c>
       <c r="C6" s="13" t="n">
-        <v>255</v>
+        <v>468</v>
       </c>
       <c r="D6" s="13" t="n">
         <v>5</v>
@@ -1391,7 +1391,7 @@
         <v>1</v>
       </c>
       <c r="C7" s="13" t="n">
-        <v>300</v>
+        <v>551</v>
       </c>
       <c r="D7" s="13" t="n">
         <v>6</v>
@@ -1405,7 +1405,7 @@
         <v>2</v>
       </c>
       <c r="C8" s="13" t="n">
-        <v>345</v>
+        <v>634</v>
       </c>
       <c r="D8" s="13" t="n">
         <v>7</v>
@@ -1419,10 +1419,10 @@
         <v>0</v>
       </c>
       <c r="C9" s="13" t="n">
-        <v>484</v>
+        <v>508</v>
       </c>
       <c r="D9" s="13" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10">
@@ -1433,10 +1433,10 @@
         <v>1</v>
       </c>
       <c r="C10" s="13" t="n">
-        <v>570</v>
+        <v>598</v>
       </c>
       <c r="D10" s="13" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11">
@@ -1447,10 +1447,10 @@
         <v>2</v>
       </c>
       <c r="C11" s="13" t="n">
-        <v>656</v>
+        <v>688</v>
       </c>
       <c r="D11" s="13" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12">
@@ -1461,10 +1461,10 @@
         <v>0</v>
       </c>
       <c r="C12" s="13" t="n">
-        <v>867</v>
+        <v>2406</v>
       </c>
       <c r="D12" s="13" t="n">
-        <v>8</v>
+        <v>26</v>
       </c>
     </row>
     <row r="13">
@@ -1475,10 +1475,10 @@
         <v>1</v>
       </c>
       <c r="C13" s="13" t="n">
-        <v>1020</v>
+        <v>2830</v>
       </c>
       <c r="D13" s="13" t="n">
-        <v>10</v>
+        <v>31</v>
       </c>
     </row>
     <row r="14">
@@ -1489,10 +1489,10 @@
         <v>2</v>
       </c>
       <c r="C14" s="13" t="n">
-        <v>1173</v>
+        <v>3254</v>
       </c>
       <c r="D14" s="13" t="n">
-        <v>11</v>
+        <v>36</v>
       </c>
     </row>
     <row r="15">
@@ -1503,10 +1503,10 @@
         <v>0</v>
       </c>
       <c r="C15" s="13" t="n">
-        <v>1721</v>
+        <v>7336</v>
       </c>
       <c r="D15" s="13" t="n">
-        <v>12</v>
+        <v>81</v>
       </c>
     </row>
     <row r="16">
@@ -1517,10 +1517,10 @@
         <v>1</v>
       </c>
       <c r="C16" s="13" t="n">
-        <v>2025</v>
+        <v>8630</v>
       </c>
       <c r="D16" s="13" t="n">
-        <v>14</v>
+        <v>95</v>
       </c>
     </row>
     <row r="17">
@@ -1531,10 +1531,10 @@
         <v>2</v>
       </c>
       <c r="C17" s="13" t="n">
-        <v>2329</v>
+        <v>9924</v>
       </c>
       <c r="D17" s="13" t="n">
-        <v>16</v>
+        <v>109</v>
       </c>
     </row>
     <row r="18">
@@ -1545,10 +1545,10 @@
         <v>0</v>
       </c>
       <c r="C18" s="13" t="n">
-        <v>3022</v>
+        <v>26868</v>
       </c>
       <c r="D18" s="13" t="n">
-        <v>21</v>
+        <v>296</v>
       </c>
     </row>
     <row r="19">
@@ -1559,10 +1559,10 @@
         <v>1</v>
       </c>
       <c r="C19" s="13" t="n">
-        <v>3555</v>
+        <v>31609</v>
       </c>
       <c r="D19" s="13" t="n">
-        <v>25</v>
+        <v>348</v>
       </c>
     </row>
     <row r="20">
@@ -1573,10 +1573,10 @@
         <v>2</v>
       </c>
       <c r="C20" s="13" t="n">
-        <v>4088</v>
+        <v>36350</v>
       </c>
       <c r="D20" s="13" t="n">
-        <v>29</v>
+        <v>400</v>
       </c>
     </row>
     <row r="21">
@@ -1587,10 +1587,10 @@
         <v>0</v>
       </c>
       <c r="C21" s="13" t="n">
-        <v>7688</v>
+        <v>95362</v>
       </c>
       <c r="D21" s="13" t="n">
-        <v>54</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="22">
@@ -1601,10 +1601,10 @@
         <v>1</v>
       </c>
       <c r="C22" s="13" t="n">
-        <v>9045</v>
+        <v>112190</v>
       </c>
       <c r="D22" s="13" t="n">
-        <v>63</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="23">
@@ -1615,10 +1615,10 @@
         <v>2</v>
       </c>
       <c r="C23" s="13" t="n">
-        <v>10402</v>
+        <v>129018</v>
       </c>
       <c r="D23" s="13" t="n">
-        <v>73</v>
+        <v>1419</v>
       </c>
     </row>
     <row r="24">
@@ -1629,10 +1629,10 @@
         <v>0</v>
       </c>
       <c r="C24" s="13" t="n">
-        <v>20094</v>
+        <v>176582</v>
       </c>
       <c r="D24" s="13" t="n">
-        <v>141</v>
+        <v>1942</v>
       </c>
     </row>
     <row r="25">
@@ -1643,10 +1643,10 @@
         <v>1</v>
       </c>
       <c r="C25" s="13" t="n">
-        <v>23640</v>
+        <v>207743</v>
       </c>
       <c r="D25" s="13" t="n">
-        <v>165</v>
+        <v>2285</v>
       </c>
     </row>
     <row r="26">
@@ -1657,10 +1657,10 @@
         <v>2</v>
       </c>
       <c r="C26" s="13" t="n">
-        <v>27186</v>
+        <v>238904</v>
       </c>
       <c r="D26" s="13" t="n">
-        <v>190</v>
+        <v>2628</v>
       </c>
     </row>
     <row r="27">
@@ -1671,10 +1671,10 @@
         <v>0</v>
       </c>
       <c r="C27" s="13" t="n">
-        <v>53716</v>
+        <v>518738</v>
       </c>
       <c r="D27" s="13" t="n">
-        <v>376</v>
+        <v>5706</v>
       </c>
     </row>
     <row r="28">
@@ -1685,10 +1685,10 @@
         <v>1</v>
       </c>
       <c r="C28" s="13" t="n">
-        <v>63195</v>
+        <v>610280</v>
       </c>
       <c r="D28" s="13" t="n">
-        <v>442</v>
+        <v>6713</v>
       </c>
     </row>
     <row r="29">
@@ -1699,10 +1699,10 @@
         <v>2</v>
       </c>
       <c r="C29" s="13" t="n">
-        <v>72674</v>
+        <v>701822</v>
       </c>
       <c r="D29" s="13" t="n">
-        <v>509</v>
+        <v>7720</v>
       </c>
     </row>
     <row r="30">
@@ -1713,10 +1713,10 @@
         <v>0</v>
       </c>
       <c r="C30" s="13" t="n">
-        <v>115606</v>
+        <v>712608</v>
       </c>
       <c r="D30" s="13" t="n">
-        <v>809</v>
+        <v>7839</v>
       </c>
     </row>
     <row r="31">
@@ -1727,10 +1727,10 @@
         <v>1</v>
       </c>
       <c r="C31" s="13" t="n">
-        <v>136007</v>
+        <v>838362</v>
       </c>
       <c r="D31" s="13" t="n">
-        <v>952</v>
+        <v>9222</v>
       </c>
     </row>
     <row r="32">
@@ -1741,10 +1741,10 @@
         <v>2</v>
       </c>
       <c r="C32" s="13" t="n">
-        <v>156408</v>
+        <v>964116</v>
       </c>
       <c r="D32" s="13" t="n">
-        <v>1095</v>
+        <v>10605</v>
       </c>
     </row>
     <row r="33">
@@ -1755,10 +1755,10 @@
         <v>0</v>
       </c>
       <c r="C33" s="13" t="n">
-        <v>216121</v>
+        <v>982499</v>
       </c>
       <c r="D33" s="13" t="n">
-        <v>1513</v>
+        <v>10807</v>
       </c>
     </row>
     <row r="34">
@@ -1769,10 +1769,10 @@
         <v>1</v>
       </c>
       <c r="C34" s="13" t="n">
-        <v>254260</v>
+        <v>1155881</v>
       </c>
       <c r="D34" s="13" t="n">
-        <v>1780</v>
+        <v>12715</v>
       </c>
     </row>
     <row r="35">
@@ -1783,10 +1783,10 @@
         <v>2</v>
       </c>
       <c r="C35" s="13" t="n">
-        <v>292399</v>
+        <v>1329263</v>
       </c>
       <c r="D35" s="13" t="n">
-        <v>2047</v>
+        <v>14622</v>
       </c>
     </row>
     <row r="36">
@@ -1797,10 +1797,10 @@
         <v>0</v>
       </c>
       <c r="C36" s="13" t="n">
-        <v>433927</v>
+        <v>1168163</v>
       </c>
       <c r="D36" s="13" t="n">
-        <v>3037</v>
+        <v>12850</v>
       </c>
     </row>
     <row r="37">
@@ -1811,10 +1811,10 @@
         <v>1</v>
       </c>
       <c r="C37" s="13" t="n">
-        <v>510502</v>
+        <v>1374309</v>
       </c>
       <c r="D37" s="13" t="n">
-        <v>3574</v>
+        <v>15117</v>
       </c>
     </row>
     <row r="38">
@@ -1825,10 +1825,10 @@
         <v>2</v>
       </c>
       <c r="C38" s="13" t="n">
-        <v>587077</v>
+        <v>1580455</v>
       </c>
       <c r="D38" s="13" t="n">
-        <v>4110</v>
+        <v>17385</v>
       </c>
     </row>
     <row r="39">
@@ -1839,10 +1839,10 @@
         <v>0</v>
       </c>
       <c r="C39" s="13" t="n">
-        <v>608195</v>
+        <v>1338056</v>
       </c>
       <c r="D39" s="13" t="n">
-        <v>4257</v>
+        <v>14719</v>
       </c>
     </row>
     <row r="40">
@@ -1853,10 +1853,10 @@
         <v>1</v>
       </c>
       <c r="C40" s="13" t="n">
-        <v>715524</v>
+        <v>1574184</v>
       </c>
       <c r="D40" s="13" t="n">
-        <v>5009</v>
+        <v>17316</v>
       </c>
     </row>
     <row r="41">
@@ -1867,10 +1867,10 @@
         <v>2</v>
       </c>
       <c r="C41" s="13" t="n">
-        <v>822853</v>
+        <v>1810312</v>
       </c>
       <c r="D41" s="13" t="n">
-        <v>5760</v>
+        <v>19913</v>
       </c>
     </row>
   </sheetData>
@@ -1998,7 +1998,7 @@
         <v>3</v>
       </c>
       <c r="E3" s="13" t="n">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="F3" s="13" t="n">
         <v>50</v>
@@ -2029,7 +2029,7 @@
         <v>5</v>
       </c>
       <c r="E4" s="13" t="n">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="F4" s="13" t="n">
         <v>80</v>
@@ -2060,7 +2060,7 @@
         <v>8</v>
       </c>
       <c r="E5" s="13" t="n">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="F5" s="13" t="n">
         <v>128</v>
@@ -2091,7 +2091,7 @@
         <v>12</v>
       </c>
       <c r="E6" s="13" t="n">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="F6" s="13" t="n">
         <v>205</v>
@@ -2122,7 +2122,7 @@
         <v>20</v>
       </c>
       <c r="E7" s="13" t="n">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="F7" s="13" t="n">
         <v>328</v>
@@ -2153,7 +2153,7 @@
         <v>31</v>
       </c>
       <c r="E8" s="13" t="n">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="F8" s="13" t="n">
         <v>524</v>
@@ -2184,7 +2184,7 @@
         <v>50</v>
       </c>
       <c r="E9" s="13" t="n">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="F9" s="13" t="n">
         <v>839</v>
@@ -2215,7 +2215,7 @@
         <v>81</v>
       </c>
       <c r="E10" s="13" t="n">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="F10" s="13" t="n">
         <v>1342</v>
@@ -2344,7 +2344,7 @@
         <v>10</v>
       </c>
       <c r="D3" s="13" t="n">
-        <v>4200</v>
+        <v>1800</v>
       </c>
       <c r="E3" s="13" t="n">
         <v>300</v>
@@ -2370,7 +2370,7 @@
         <v>20</v>
       </c>
       <c r="D4" s="13" t="n">
-        <v>6720</v>
+        <v>2880</v>
       </c>
       <c r="E4" s="13" t="n">
         <v>480</v>
@@ -2396,7 +2396,7 @@
         <v>30</v>
       </c>
       <c r="D5" s="13" t="n">
-        <v>10752</v>
+        <v>4608</v>
       </c>
       <c r="E5" s="13" t="n">
         <v>768</v>
@@ -2422,7 +2422,7 @@
         <v>40</v>
       </c>
       <c r="D6" s="13" t="n">
-        <v>17203</v>
+        <v>7373</v>
       </c>
       <c r="E6" s="13" t="n">
         <v>1229</v>
@@ -2448,7 +2448,7 @@
         <v>50</v>
       </c>
       <c r="D7" s="13" t="n">
-        <v>27525</v>
+        <v>11796</v>
       </c>
       <c r="E7" s="13" t="n">
         <v>1966</v>
@@ -2474,7 +2474,7 @@
         <v>60</v>
       </c>
       <c r="D8" s="13" t="n">
-        <v>44040</v>
+        <v>18874</v>
       </c>
       <c r="E8" s="13" t="n">
         <v>3146</v>
@@ -2500,7 +2500,7 @@
         <v>70</v>
       </c>
       <c r="D9" s="13" t="n">
-        <v>70464</v>
+        <v>30199</v>
       </c>
       <c r="E9" s="13" t="n">
         <v>5033</v>
@@ -2526,7 +2526,7 @@
         <v>80</v>
       </c>
       <c r="D10" s="13" t="n">
-        <v>112743</v>
+        <v>48318</v>
       </c>
       <c r="E10" s="13" t="n">
         <v>8053</v>
@@ -2650,19 +2650,19 @@
         <v>5</v>
       </c>
       <c r="C3" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D3" s="13" t="n">
-        <v>50</v>
+        <v>120</v>
       </c>
       <c r="E3" s="13" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="F3" s="13" t="n">
         <v>0</v>
       </c>
       <c r="G3" s="13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H3" s="14">
         <f>B3*D3+E3*((B3-1)*B3/2)</f>
@@ -2677,13 +2677,13 @@
         <v>10</v>
       </c>
       <c r="C4" s="13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D4" s="13" t="n">
         <v>50</v>
       </c>
       <c r="E4" s="13" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F4" s="13" t="n">
         <v>3</v>
@@ -2704,19 +2704,19 @@
         <v>6</v>
       </c>
       <c r="C5" s="13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D5" s="13" t="n">
-        <v>108</v>
+        <v>477</v>
       </c>
       <c r="E5" s="13" t="n">
-        <v>27</v>
+        <v>119</v>
       </c>
       <c r="F5" s="13" t="n">
         <v>1</v>
       </c>
       <c r="G5" s="13" t="n">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="H5" s="14">
         <f>B5*D5+E5*((B5-1)*B5/2)</f>
@@ -2731,13 +2731,13 @@
         <v>4</v>
       </c>
       <c r="C6" s="13" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D6" s="13" t="n">
-        <v>382</v>
+        <v>2591</v>
       </c>
       <c r="E6" s="13" t="n">
-        <v>95</v>
+        <v>648</v>
       </c>
       <c r="F6" s="13" t="n">
         <v>4</v>
@@ -2758,13 +2758,13 @@
         <v>9</v>
       </c>
       <c r="C7" s="13" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D7" s="13" t="n">
-        <v>208</v>
+        <v>2900</v>
       </c>
       <c r="E7" s="13" t="n">
-        <v>52</v>
+        <v>725</v>
       </c>
       <c r="F7" s="13" t="n">
         <v>2</v>
@@ -2785,13 +2785,13 @@
         <v>8</v>
       </c>
       <c r="C8" s="13" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D8" s="13" t="n">
-        <v>630</v>
+        <v>12340</v>
       </c>
       <c r="E8" s="13" t="n">
-        <v>158</v>
+        <v>3085</v>
       </c>
       <c r="F8" s="13" t="n">
         <v>3</v>
@@ -2812,19 +2812,19 @@
         <v>5</v>
       </c>
       <c r="C9" s="13" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D9" s="13" t="n">
-        <v>3300</v>
+        <v>45700</v>
       </c>
       <c r="E9" s="13" t="n">
-        <v>825</v>
+        <v>11425</v>
       </c>
       <c r="F9" s="13" t="n">
         <v>1</v>
       </c>
       <c r="G9" s="13" t="n">
-        <v>189</v>
+        <v>1662</v>
       </c>
       <c r="H9" s="14">
         <f>B9*D9+E9*((B9-1)*B9/2)</f>
@@ -2839,13 +2839,13 @@
         <v>9</v>
       </c>
       <c r="C10" s="13" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D10" s="13" t="n">
-        <v>3683</v>
+        <v>55942</v>
       </c>
       <c r="E10" s="13" t="n">
-        <v>921</v>
+        <v>13985</v>
       </c>
       <c r="F10" s="13" t="n">
         <v>5</v>
@@ -2866,13 +2866,13 @@
         <v>9</v>
       </c>
       <c r="C11" s="13" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D11" s="13" t="n">
-        <v>7933</v>
+        <v>76850</v>
       </c>
       <c r="E11" s="13" t="n">
-        <v>1983</v>
+        <v>19212</v>
       </c>
       <c r="F11" s="13" t="n">
         <v>2</v>
@@ -2893,13 +2893,13 @@
         <v>4</v>
       </c>
       <c r="C12" s="13" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D12" s="13" t="n">
-        <v>48545</v>
+        <v>346773</v>
       </c>
       <c r="E12" s="13" t="n">
-        <v>12136</v>
+        <v>86693</v>
       </c>
       <c r="F12" s="13" t="n">
         <v>3</v>
@@ -2920,13 +2920,13 @@
         <v>12</v>
       </c>
       <c r="C13" s="13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D13" s="13" t="n">
-        <v>18811</v>
+        <v>79563</v>
       </c>
       <c r="E13" s="13" t="n">
-        <v>4703</v>
+        <v>19891</v>
       </c>
       <c r="F13" s="13" t="n">
         <v>4</v>
@@ -2947,19 +2947,19 @@
         <v>7</v>
       </c>
       <c r="C14" s="13" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D14" s="13" t="n">
-        <v>61335</v>
+        <v>212033</v>
       </c>
       <c r="E14" s="13" t="n">
-        <v>15334</v>
+        <v>53008</v>
       </c>
       <c r="F14" s="13" t="n">
         <v>0</v>
       </c>
       <c r="G14" s="13" t="n">
-        <v>3816</v>
+        <v>8396</v>
       </c>
       <c r="H14" s="14">
         <f>B14*D14+E14*((B14-1)*B14/2)</f>

--- a/DataTable/내일할래_데이터테이블.xlsx
+++ b/DataTable/내일할래_데이터테이블.xlsx
@@ -1128,10 +1128,10 @@
         <v>0</v>
       </c>
       <c r="B3" s="13" t="n">
-        <v>3335</v>
+        <v>1373</v>
       </c>
       <c r="C3" s="13" t="n">
-        <v>100</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="4">
@@ -1139,10 +1139,10 @@
         <v>1</v>
       </c>
       <c r="B4" s="13" t="n">
-        <v>3602</v>
+        <v>2377</v>
       </c>
       <c r="C4" s="13" t="n">
-        <v>300</v>
+        <v>2800</v>
       </c>
     </row>
     <row r="5">
@@ -1150,10 +1150,10 @@
         <v>2</v>
       </c>
       <c r="B5" s="13" t="n">
-        <v>25228</v>
+        <v>6013</v>
       </c>
       <c r="C5" s="13" t="n">
-        <v>350</v>
+        <v>7100</v>
       </c>
     </row>
     <row r="6">
@@ -1161,10 +1161,10 @@
         <v>3</v>
       </c>
       <c r="B6" s="13" t="n">
-        <v>73320</v>
+        <v>18973</v>
       </c>
       <c r="C6" s="13" t="n">
-        <v>1550</v>
+        <v>22350</v>
       </c>
     </row>
     <row r="7">
@@ -1172,10 +1172,10 @@
         <v>4</v>
       </c>
       <c r="B7" s="13" t="n">
-        <v>250629</v>
+        <v>65353</v>
       </c>
       <c r="C7" s="13" t="n">
-        <v>4750</v>
+        <v>77017</v>
       </c>
     </row>
     <row r="8">
@@ -1183,10 +1183,10 @@
         <v>5</v>
       </c>
       <c r="B8" s="13" t="n">
-        <v>821776</v>
+        <v>220356</v>
       </c>
       <c r="C8" s="13" t="n">
-        <v>17400</v>
+        <v>259700</v>
       </c>
     </row>
     <row r="9">
@@ -1194,10 +1194,10 @@
         <v>6</v>
       </c>
       <c r="B9" s="13" t="n">
-        <v>590049</v>
+        <v>668260</v>
       </c>
       <c r="C9" s="13" t="n">
-        <v>61700</v>
+        <v>787600</v>
       </c>
     </row>
     <row r="10">
@@ -1205,10 +1205,10 @@
         <v>7</v>
       </c>
       <c r="B10" s="13" t="n">
-        <v>1758449</v>
+        <v>1716202</v>
       </c>
       <c r="C10" s="13" t="n">
-        <v>114250</v>
+        <v>2022650</v>
       </c>
     </row>
     <row r="11">
@@ -1216,10 +1216,10 @@
         <v>8</v>
       </c>
       <c r="B11" s="13" t="n">
-        <v>210988</v>
+        <v>3601121</v>
       </c>
       <c r="C11" s="13" t="n">
-        <v>335650</v>
+        <v>4244183</v>
       </c>
     </row>
     <row r="12">
@@ -1227,10 +1227,10 @@
         <v>9</v>
       </c>
       <c r="B12" s="13" t="n">
-        <v>2802589</v>
+        <v>6103807</v>
       </c>
       <c r="C12" s="13" t="n">
-        <v>461100</v>
+        <v>7193767</v>
       </c>
     </row>
     <row r="13">
@@ -1238,10 +1238,10 @@
         <v>10</v>
       </c>
       <c r="B13" s="13" t="n">
-        <v>4668293</v>
+        <v>8466586</v>
       </c>
       <c r="C13" s="13" t="n">
-        <v>635750</v>
+        <v>9978483</v>
       </c>
     </row>
     <row r="14">
@@ -1249,10 +1249,10 @@
         <v>11</v>
       </c>
       <c r="B14" s="13" t="n">
-        <v>6598746</v>
+        <v>9977324</v>
       </c>
       <c r="C14" s="13" t="n">
-        <v>755850</v>
+        <v>11759000</v>
       </c>
     </row>
     <row r="15">
@@ -1260,10 +1260,10 @@
         <v>12</v>
       </c>
       <c r="B15" s="13" t="n">
-        <v>11019739</v>
+        <v>10626129</v>
       </c>
       <c r="C15" s="13" t="n">
-        <v>865800</v>
+        <v>12523650</v>
       </c>
     </row>
   </sheetData>
@@ -1335,10 +1335,10 @@
         <v>0</v>
       </c>
       <c r="C3" s="13" t="n">
-        <v>140</v>
+        <v>111</v>
       </c>
       <c r="D3" s="13" t="n">
-        <v>2</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4">
@@ -1349,10 +1349,10 @@
         <v>1</v>
       </c>
       <c r="C4" s="13" t="n">
-        <v>165</v>
+        <v>131</v>
       </c>
       <c r="D4" s="13" t="n">
-        <v>2</v>
+        <v>32</v>
       </c>
     </row>
     <row r="5">
@@ -1363,10 +1363,10 @@
         <v>2</v>
       </c>
       <c r="C5" s="13" t="n">
-        <v>190</v>
+        <v>150</v>
       </c>
       <c r="D5" s="13" t="n">
-        <v>2</v>
+        <v>37</v>
       </c>
     </row>
     <row r="6">
@@ -1377,10 +1377,10 @@
         <v>0</v>
       </c>
       <c r="C6" s="13" t="n">
-        <v>468</v>
+        <v>192</v>
       </c>
       <c r="D6" s="13" t="n">
-        <v>5</v>
+        <v>48</v>
       </c>
     </row>
     <row r="7">
@@ -1391,10 +1391,10 @@
         <v>1</v>
       </c>
       <c r="C7" s="13" t="n">
-        <v>551</v>
+        <v>226</v>
       </c>
       <c r="D7" s="13" t="n">
-        <v>6</v>
+        <v>56</v>
       </c>
     </row>
     <row r="8">
@@ -1405,10 +1405,10 @@
         <v>2</v>
       </c>
       <c r="C8" s="13" t="n">
-        <v>634</v>
+        <v>260</v>
       </c>
       <c r="D8" s="13" t="n">
-        <v>7</v>
+        <v>64</v>
       </c>
     </row>
     <row r="9">
@@ -1419,10 +1419,10 @@
         <v>0</v>
       </c>
       <c r="C9" s="13" t="n">
-        <v>508</v>
+        <v>487</v>
       </c>
       <c r="D9" s="13" t="n">
-        <v>6</v>
+        <v>121</v>
       </c>
     </row>
     <row r="10">
@@ -1433,10 +1433,10 @@
         <v>1</v>
       </c>
       <c r="C10" s="13" t="n">
-        <v>598</v>
+        <v>573</v>
       </c>
       <c r="D10" s="13" t="n">
-        <v>7</v>
+        <v>142</v>
       </c>
     </row>
     <row r="11">
@@ -1447,10 +1447,10 @@
         <v>2</v>
       </c>
       <c r="C11" s="13" t="n">
-        <v>688</v>
+        <v>659</v>
       </c>
       <c r="D11" s="13" t="n">
-        <v>8</v>
+        <v>163</v>
       </c>
     </row>
     <row r="12">
@@ -1461,10 +1461,10 @@
         <v>0</v>
       </c>
       <c r="C12" s="13" t="n">
-        <v>2406</v>
+        <v>1536</v>
       </c>
       <c r="D12" s="13" t="n">
-        <v>26</v>
+        <v>380</v>
       </c>
     </row>
     <row r="13">
@@ -1475,10 +1475,10 @@
         <v>1</v>
       </c>
       <c r="C13" s="13" t="n">
-        <v>2830</v>
+        <v>1807</v>
       </c>
       <c r="D13" s="13" t="n">
-        <v>31</v>
+        <v>447</v>
       </c>
     </row>
     <row r="14">
@@ -1489,10 +1489,10 @@
         <v>2</v>
       </c>
       <c r="C14" s="13" t="n">
-        <v>3254</v>
+        <v>2078</v>
       </c>
       <c r="D14" s="13" t="n">
-        <v>36</v>
+        <v>514</v>
       </c>
     </row>
     <row r="15">
@@ -1503,10 +1503,10 @@
         <v>0</v>
       </c>
       <c r="C15" s="13" t="n">
-        <v>7336</v>
+        <v>5290</v>
       </c>
       <c r="D15" s="13" t="n">
-        <v>81</v>
+        <v>1309</v>
       </c>
     </row>
     <row r="16">
@@ -1517,10 +1517,10 @@
         <v>1</v>
       </c>
       <c r="C16" s="13" t="n">
-        <v>8630</v>
+        <v>6224</v>
       </c>
       <c r="D16" s="13" t="n">
-        <v>95</v>
+        <v>1540</v>
       </c>
     </row>
     <row r="17">
@@ -1531,10 +1531,10 @@
         <v>2</v>
       </c>
       <c r="C17" s="13" t="n">
-        <v>9924</v>
+        <v>7158</v>
       </c>
       <c r="D17" s="13" t="n">
-        <v>109</v>
+        <v>1772</v>
       </c>
     </row>
     <row r="18">
@@ -1545,10 +1545,10 @@
         <v>0</v>
       </c>
       <c r="C18" s="13" t="n">
-        <v>26868</v>
+        <v>17838</v>
       </c>
       <c r="D18" s="13" t="n">
-        <v>296</v>
+        <v>4415</v>
       </c>
     </row>
     <row r="19">
@@ -1559,10 +1559,10 @@
         <v>1</v>
       </c>
       <c r="C19" s="13" t="n">
-        <v>31609</v>
+        <v>20986</v>
       </c>
       <c r="D19" s="13" t="n">
-        <v>348</v>
+        <v>5194</v>
       </c>
     </row>
     <row r="20">
@@ -1573,10 +1573,10 @@
         <v>2</v>
       </c>
       <c r="C20" s="13" t="n">
-        <v>36350</v>
+        <v>24134</v>
       </c>
       <c r="D20" s="13" t="n">
-        <v>400</v>
+        <v>5973</v>
       </c>
     </row>
     <row r="21">
@@ -1587,10 +1587,10 @@
         <v>0</v>
       </c>
       <c r="C21" s="13" t="n">
-        <v>95362</v>
+        <v>54097</v>
       </c>
       <c r="D21" s="13" t="n">
-        <v>1049</v>
+        <v>13389</v>
       </c>
     </row>
     <row r="22">
@@ -1601,10 +1601,10 @@
         <v>1</v>
       </c>
       <c r="C22" s="13" t="n">
-        <v>112190</v>
+        <v>63644</v>
       </c>
       <c r="D22" s="13" t="n">
-        <v>1234</v>
+        <v>15752</v>
       </c>
     </row>
     <row r="23">
@@ -1615,10 +1615,10 @@
         <v>2</v>
       </c>
       <c r="C23" s="13" t="n">
-        <v>129018</v>
+        <v>73190</v>
       </c>
       <c r="D23" s="13" t="n">
-        <v>1419</v>
+        <v>18115</v>
       </c>
     </row>
     <row r="24">
@@ -1629,10 +1629,10 @@
         <v>0</v>
       </c>
       <c r="C24" s="13" t="n">
-        <v>176582</v>
+        <v>138931</v>
       </c>
       <c r="D24" s="13" t="n">
-        <v>1942</v>
+        <v>34385</v>
       </c>
     </row>
     <row r="25">
@@ -1643,10 +1643,10 @@
         <v>1</v>
       </c>
       <c r="C25" s="13" t="n">
-        <v>207743</v>
+        <v>163448</v>
       </c>
       <c r="D25" s="13" t="n">
-        <v>2285</v>
+        <v>40453</v>
       </c>
     </row>
     <row r="26">
@@ -1657,10 +1657,10 @@
         <v>2</v>
       </c>
       <c r="C26" s="13" t="n">
-        <v>238904</v>
+        <v>187965</v>
       </c>
       <c r="D26" s="13" t="n">
-        <v>2628</v>
+        <v>46521</v>
       </c>
     </row>
     <row r="27">
@@ -1671,10 +1671,10 @@
         <v>0</v>
       </c>
       <c r="C27" s="13" t="n">
-        <v>518738</v>
+        <v>291519</v>
       </c>
       <c r="D27" s="13" t="n">
-        <v>5706</v>
+        <v>72151</v>
       </c>
     </row>
     <row r="28">
@@ -1685,10 +1685,10 @@
         <v>1</v>
       </c>
       <c r="C28" s="13" t="n">
-        <v>610280</v>
+        <v>342964</v>
       </c>
       <c r="D28" s="13" t="n">
-        <v>6713</v>
+        <v>84884</v>
       </c>
     </row>
     <row r="29">
@@ -1699,10 +1699,10 @@
         <v>2</v>
       </c>
       <c r="C29" s="13" t="n">
-        <v>701822</v>
+        <v>394408</v>
       </c>
       <c r="D29" s="13" t="n">
-        <v>7720</v>
+        <v>97616</v>
       </c>
     </row>
     <row r="30">
@@ -1713,10 +1713,10 @@
         <v>0</v>
       </c>
       <c r="C30" s="13" t="n">
-        <v>712608</v>
+        <v>494118</v>
       </c>
       <c r="D30" s="13" t="n">
-        <v>7839</v>
+        <v>122294</v>
       </c>
     </row>
     <row r="31">
@@ -1727,10 +1727,10 @@
         <v>1</v>
       </c>
       <c r="C31" s="13" t="n">
-        <v>838362</v>
+        <v>581315</v>
       </c>
       <c r="D31" s="13" t="n">
-        <v>9222</v>
+        <v>143875</v>
       </c>
     </row>
     <row r="32">
@@ -1741,10 +1741,10 @@
         <v>2</v>
       </c>
       <c r="C32" s="13" t="n">
-        <v>964116</v>
+        <v>668512</v>
       </c>
       <c r="D32" s="13" t="n">
-        <v>10605</v>
+        <v>165457</v>
       </c>
     </row>
     <row r="33">
@@ -1755,10 +1755,10 @@
         <v>0</v>
       </c>
       <c r="C33" s="13" t="n">
-        <v>982499</v>
+        <v>685390</v>
       </c>
       <c r="D33" s="13" t="n">
-        <v>10807</v>
+        <v>169634</v>
       </c>
     </row>
     <row r="34">
@@ -1769,10 +1769,10 @@
         <v>1</v>
       </c>
       <c r="C34" s="13" t="n">
-        <v>1155881</v>
+        <v>806342</v>
       </c>
       <c r="D34" s="13" t="n">
-        <v>12715</v>
+        <v>199570</v>
       </c>
     </row>
     <row r="35">
@@ -1783,10 +1783,10 @@
         <v>2</v>
       </c>
       <c r="C35" s="13" t="n">
-        <v>1329263</v>
+        <v>927293</v>
       </c>
       <c r="D35" s="13" t="n">
-        <v>14622</v>
+        <v>229505</v>
       </c>
     </row>
     <row r="36">
@@ -1797,10 +1797,10 @@
         <v>0</v>
       </c>
       <c r="C36" s="13" t="n">
-        <v>1168163</v>
+        <v>807688</v>
       </c>
       <c r="D36" s="13" t="n">
-        <v>12850</v>
+        <v>199903</v>
       </c>
     </row>
     <row r="37">
@@ -1811,10 +1811,10 @@
         <v>1</v>
       </c>
       <c r="C37" s="13" t="n">
-        <v>1374309</v>
+        <v>950221</v>
       </c>
       <c r="D37" s="13" t="n">
-        <v>15117</v>
+        <v>235180</v>
       </c>
     </row>
     <row r="38">
@@ -1825,10 +1825,10 @@
         <v>2</v>
       </c>
       <c r="C38" s="13" t="n">
-        <v>1580455</v>
+        <v>1092755</v>
       </c>
       <c r="D38" s="13" t="n">
-        <v>17385</v>
+        <v>270457</v>
       </c>
     </row>
     <row r="39">
@@ -1839,10 +1839,10 @@
         <v>0</v>
       </c>
       <c r="C39" s="13" t="n">
-        <v>1338056</v>
+        <v>860210</v>
       </c>
       <c r="D39" s="13" t="n">
-        <v>14719</v>
+        <v>212902</v>
       </c>
     </row>
     <row r="40">
@@ -1853,10 +1853,10 @@
         <v>1</v>
       </c>
       <c r="C40" s="13" t="n">
-        <v>1574184</v>
+        <v>1012012</v>
       </c>
       <c r="D40" s="13" t="n">
-        <v>17316</v>
+        <v>250473</v>
       </c>
     </row>
     <row r="41">
@@ -1867,10 +1867,10 @@
         <v>2</v>
       </c>
       <c r="C41" s="13" t="n">
-        <v>1810312</v>
+        <v>1163814</v>
       </c>
       <c r="D41" s="13" t="n">
-        <v>19913</v>
+        <v>288044</v>
       </c>
     </row>
   </sheetData>
@@ -2001,10 +2001,10 @@
         <v>300</v>
       </c>
       <c r="F3" s="13" t="n">
+        <v>500</v>
+      </c>
+      <c r="G3" s="13" t="n">
         <v>50</v>
-      </c>
-      <c r="G3" s="13" t="n">
-        <v>5</v>
       </c>
       <c r="H3" s="14">
         <f>C3+(E3-1)*D3</f>
@@ -2020,7 +2020,7 @@
         <v>1</v>
       </c>
       <c r="B4" s="13" t="n">
-        <v>800</v>
+        <v>8000</v>
       </c>
       <c r="C4" s="13" t="n">
         <v>16</v>
@@ -2032,10 +2032,10 @@
         <v>300</v>
       </c>
       <c r="F4" s="13" t="n">
+        <v>800</v>
+      </c>
+      <c r="G4" s="13" t="n">
         <v>80</v>
-      </c>
-      <c r="G4" s="13" t="n">
-        <v>8</v>
       </c>
       <c r="H4" s="14">
         <f>C4+(E4-1)*D4</f>
@@ -2051,7 +2051,7 @@
         <v>2</v>
       </c>
       <c r="B5" s="13" t="n">
-        <v>1280</v>
+        <v>12800</v>
       </c>
       <c r="C5" s="13" t="n">
         <v>26</v>
@@ -2063,10 +2063,10 @@
         <v>300</v>
       </c>
       <c r="F5" s="13" t="n">
-        <v>128</v>
+        <v>1280</v>
       </c>
       <c r="G5" s="13" t="n">
-        <v>13</v>
+        <v>130</v>
       </c>
       <c r="H5" s="14">
         <f>C5+(E5-1)*D5</f>
@@ -2082,7 +2082,7 @@
         <v>3</v>
       </c>
       <c r="B6" s="13" t="n">
-        <v>2048</v>
+        <v>20480</v>
       </c>
       <c r="C6" s="13" t="n">
         <v>41</v>
@@ -2094,10 +2094,10 @@
         <v>300</v>
       </c>
       <c r="F6" s="13" t="n">
-        <v>205</v>
+        <v>2050</v>
       </c>
       <c r="G6" s="13" t="n">
-        <v>20</v>
+        <v>200</v>
       </c>
       <c r="H6">
         <f>C6+(E6-1)*D6</f>
@@ -2113,7 +2113,7 @@
         <v>4</v>
       </c>
       <c r="B7" s="13" t="n">
-        <v>3277</v>
+        <v>32770</v>
       </c>
       <c r="C7" s="13" t="n">
         <v>66</v>
@@ -2125,10 +2125,10 @@
         <v>300</v>
       </c>
       <c r="F7" s="13" t="n">
-        <v>328</v>
+        <v>3280</v>
       </c>
       <c r="G7" s="13" t="n">
-        <v>33</v>
+        <v>330</v>
       </c>
       <c r="H7">
         <f>C7+(E7-1)*D7</f>
@@ -2144,7 +2144,7 @@
         <v>5</v>
       </c>
       <c r="B8" s="13" t="n">
-        <v>5243</v>
+        <v>52430</v>
       </c>
       <c r="C8" s="13" t="n">
         <v>105</v>
@@ -2156,10 +2156,10 @@
         <v>300</v>
       </c>
       <c r="F8" s="13" t="n">
-        <v>524</v>
+        <v>5240</v>
       </c>
       <c r="G8" s="13" t="n">
-        <v>52</v>
+        <v>520</v>
       </c>
       <c r="H8">
         <f>C8+(E8-1)*D8</f>
@@ -2175,7 +2175,7 @@
         <v>6</v>
       </c>
       <c r="B9" s="13" t="n">
-        <v>8389</v>
+        <v>83890</v>
       </c>
       <c r="C9" s="13" t="n">
         <v>168</v>
@@ -2187,10 +2187,10 @@
         <v>300</v>
       </c>
       <c r="F9" s="13" t="n">
-        <v>839</v>
+        <v>8390</v>
       </c>
       <c r="G9" s="13" t="n">
-        <v>84</v>
+        <v>840</v>
       </c>
       <c r="H9">
         <f>C9+(E9-1)*D9</f>
@@ -2206,7 +2206,7 @@
         <v>7</v>
       </c>
       <c r="B10" s="13" t="n">
-        <v>13422</v>
+        <v>134220</v>
       </c>
       <c r="C10" s="13" t="n">
         <v>268</v>
@@ -2218,10 +2218,10 @@
         <v>300</v>
       </c>
       <c r="F10" s="13" t="n">
-        <v>1342</v>
+        <v>13420</v>
       </c>
       <c r="G10" s="13" t="n">
-        <v>134</v>
+        <v>1340</v>
       </c>
       <c r="H10">
         <f>C10+(E10-1)*D10</f>
@@ -2344,7 +2344,7 @@
         <v>10</v>
       </c>
       <c r="D3" s="13" t="n">
-        <v>1800</v>
+        <v>18000</v>
       </c>
       <c r="E3" s="13" t="n">
         <v>300</v>
@@ -2370,7 +2370,7 @@
         <v>20</v>
       </c>
       <c r="D4" s="13" t="n">
-        <v>2880</v>
+        <v>28800</v>
       </c>
       <c r="E4" s="13" t="n">
         <v>480</v>
@@ -2396,7 +2396,7 @@
         <v>30</v>
       </c>
       <c r="D5" s="13" t="n">
-        <v>4608</v>
+        <v>46080</v>
       </c>
       <c r="E5" s="13" t="n">
         <v>768</v>
@@ -2422,7 +2422,7 @@
         <v>40</v>
       </c>
       <c r="D6" s="13" t="n">
-        <v>7373</v>
+        <v>73730</v>
       </c>
       <c r="E6" s="13" t="n">
         <v>1229</v>
@@ -2448,7 +2448,7 @@
         <v>50</v>
       </c>
       <c r="D7" s="13" t="n">
-        <v>11796</v>
+        <v>117960</v>
       </c>
       <c r="E7" s="13" t="n">
         <v>1966</v>
@@ -2474,7 +2474,7 @@
         <v>60</v>
       </c>
       <c r="D8" s="13" t="n">
-        <v>18874</v>
+        <v>188740</v>
       </c>
       <c r="E8" s="13" t="n">
         <v>3146</v>
@@ -2500,7 +2500,7 @@
         <v>70</v>
       </c>
       <c r="D9" s="13" t="n">
-        <v>30199</v>
+        <v>301990</v>
       </c>
       <c r="E9" s="13" t="n">
         <v>5033</v>
@@ -2526,7 +2526,7 @@
         <v>80</v>
       </c>
       <c r="D10" s="13" t="n">
-        <v>48318</v>
+        <v>483180</v>
       </c>
       <c r="E10" s="13" t="n">
         <v>8053</v>
@@ -2653,10 +2653,10 @@
         <v>1</v>
       </c>
       <c r="D3" s="13" t="n">
-        <v>120</v>
+        <v>1200</v>
       </c>
       <c r="E3" s="13" t="n">
-        <v>30</v>
+        <v>300</v>
       </c>
       <c r="F3" s="13" t="n">
         <v>0</v>
@@ -2680,10 +2680,10 @@
         <v>2</v>
       </c>
       <c r="D4" s="13" t="n">
-        <v>50</v>
+        <v>500</v>
       </c>
       <c r="E4" s="13" t="n">
-        <v>12</v>
+        <v>120</v>
       </c>
       <c r="F4" s="13" t="n">
         <v>3</v>
@@ -2707,10 +2707,10 @@
         <v>3</v>
       </c>
       <c r="D5" s="13" t="n">
-        <v>477</v>
+        <v>4770</v>
       </c>
       <c r="E5" s="13" t="n">
-        <v>119</v>
+        <v>1190</v>
       </c>
       <c r="F5" s="13" t="n">
         <v>1</v>
@@ -2734,10 +2734,10 @@
         <v>4</v>
       </c>
       <c r="D6" s="13" t="n">
-        <v>2591</v>
+        <v>25910</v>
       </c>
       <c r="E6" s="13" t="n">
-        <v>648</v>
+        <v>6480</v>
       </c>
       <c r="F6" s="13" t="n">
         <v>4</v>
@@ -2761,10 +2761,10 @@
         <v>5</v>
       </c>
       <c r="D7" s="13" t="n">
-        <v>2900</v>
+        <v>29000</v>
       </c>
       <c r="E7" s="13" t="n">
-        <v>725</v>
+        <v>7250</v>
       </c>
       <c r="F7" s="13" t="n">
         <v>2</v>
@@ -2788,10 +2788,10 @@
         <v>6</v>
       </c>
       <c r="D8" s="13" t="n">
-        <v>12340</v>
+        <v>123400</v>
       </c>
       <c r="E8" s="13" t="n">
-        <v>3085</v>
+        <v>30850</v>
       </c>
       <c r="F8" s="13" t="n">
         <v>3</v>
@@ -2815,10 +2815,10 @@
         <v>7</v>
       </c>
       <c r="D9" s="13" t="n">
-        <v>45700</v>
+        <v>457000</v>
       </c>
       <c r="E9" s="13" t="n">
-        <v>11425</v>
+        <v>114250</v>
       </c>
       <c r="F9" s="13" t="n">
         <v>1</v>
@@ -2842,10 +2842,10 @@
         <v>8</v>
       </c>
       <c r="D10" s="13" t="n">
-        <v>55942</v>
+        <v>559420</v>
       </c>
       <c r="E10" s="13" t="n">
-        <v>13985</v>
+        <v>139850</v>
       </c>
       <c r="F10" s="13" t="n">
         <v>5</v>
@@ -2869,10 +2869,10 @@
         <v>9</v>
       </c>
       <c r="D11" s="13" t="n">
-        <v>76850</v>
+        <v>768500</v>
       </c>
       <c r="E11" s="13" t="n">
-        <v>19212</v>
+        <v>192120</v>
       </c>
       <c r="F11" s="13" t="n">
         <v>2</v>
@@ -2896,10 +2896,10 @@
         <v>10</v>
       </c>
       <c r="D12" s="13" t="n">
-        <v>346773</v>
+        <v>3467730</v>
       </c>
       <c r="E12" s="13" t="n">
-        <v>86693</v>
+        <v>866930</v>
       </c>
       <c r="F12" s="13" t="n">
         <v>3</v>
@@ -2923,10 +2923,10 @@
         <v>11</v>
       </c>
       <c r="D13" s="13" t="n">
-        <v>79563</v>
+        <v>795630</v>
       </c>
       <c r="E13" s="13" t="n">
-        <v>19891</v>
+        <v>198910</v>
       </c>
       <c r="F13" s="13" t="n">
         <v>4</v>
@@ -2950,10 +2950,10 @@
         <v>12</v>
       </c>
       <c r="D14" s="13" t="n">
-        <v>212033</v>
+        <v>2120330</v>
       </c>
       <c r="E14" s="13" t="n">
-        <v>53008</v>
+        <v>530080</v>
       </c>
       <c r="F14" s="13" t="n">
         <v>0</v>
